--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Price list" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="discount" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5763,4 +5764,444 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Party Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Clean Party</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Discount 5%</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Discount 12%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Discount 18%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Discount 28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>APEX ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>APEX ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BLINK COMMERCE PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BLINK COMMERCE PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.47619</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.533898</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jupiter Kart Private Limited</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jupiter Kart Private Limited</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.47619</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.533898</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Moksh Enterprises Private Limited</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Moksh Enterprises Private Limited</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.47619</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.533898</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cloudkart Ventures Private Limited</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cloudkart Ventures Private Limited</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.47619</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.533898</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cloudstore Retail Private Limited</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cloudstore Retail Private Limited</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.47619</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.533898</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PJTJ Technologies Private Limited</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PJTJ Technologies Private Limited</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.47619</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.533898</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BABA SALES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BABA SALES</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5339</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LOOKS AND MUCH MORE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LOOKS AND MUCH MORE</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5339</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HAI BABY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HAI BABY</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.5339</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TEJAL INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TEJAL INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5339</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SPILLBOX INNOVATION PRIVATE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SPILLBOX INNOVATION PRIVATE</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5763</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KITSONS KONDAPUR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KITSONS KONDAPUR</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4915</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SAI TAK AND CO (Boston Books,Stationery &amp; Toys)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SAI TAK AND CO (Boston Books,Stationery &amp; Toys)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4915</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KITSONS GACHIBOWLI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KITSONS GACHIBOWLI</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.4915</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KITSONS GOLDEN MILE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KITSONS GOLDEN MILE</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.4915</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KITSONS KOKAPET</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KITSONS KOKAPET</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.4915</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I171"/>
+  <dimension ref="A1:I175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,8 +476,10 @@
       <c r="C2" t="n">
         <v>969</v>
       </c>
-      <c r="D2" t="n">
-        <v>95030020</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>0.05</v>
@@ -487,12 +489,13 @@
           <t>SMRT1011</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>8908006537105</v>
-      </c>
-      <c r="H2" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8908006537105</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -506,8 +509,10 @@
       <c r="C3" t="n">
         <v>1059</v>
       </c>
-      <c r="D3" t="n">
-        <v>95030020</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E3" t="n">
         <v>0.05</v>
@@ -517,14 +522,17 @@
           <t>SMRT1012</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>8908006537112</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8908006537112</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>8606916</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -538,8 +546,10 @@
       <c r="C4" t="n">
         <v>969</v>
       </c>
-      <c r="D4" t="n">
-        <v>95030020</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E4" t="n">
         <v>0.05</v>
@@ -549,12 +559,13 @@
           <t>SMRT1013</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>8908006537129</v>
-      </c>
-      <c r="H4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8908006537129</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -568,8 +579,10 @@
       <c r="C5" t="n">
         <v>969</v>
       </c>
-      <c r="D5" t="n">
-        <v>95030020</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E5" t="n">
         <v>0.05</v>
@@ -579,12 +592,13 @@
           <t>SMRT1014</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>8908006537136</v>
-      </c>
-      <c r="H5" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8908006537136</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -598,8 +612,10 @@
       <c r="C6" t="n">
         <v>1159</v>
       </c>
-      <c r="D6" t="n">
-        <v>95030020</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E6" t="n">
         <v>0.05</v>
@@ -609,12 +625,13 @@
           <t>SMRT1017</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>8908006537167</v>
-      </c>
-      <c r="H6" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8908006537167</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -628,8 +645,10 @@
       <c r="C7" t="n">
         <v>1349</v>
       </c>
-      <c r="D7" t="n">
-        <v>95030020</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E7" t="n">
         <v>0.05</v>
@@ -639,12 +658,13 @@
           <t>SMRT1018</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>8908006537174</v>
-      </c>
-      <c r="H7" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8908006537174</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -658,8 +678,10 @@
       <c r="C8" t="n">
         <v>339</v>
       </c>
-      <c r="D8" t="n">
-        <v>95030020</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E8" t="n">
         <v>0.05</v>
@@ -669,12 +691,13 @@
           <t>SMRT1021</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>8908006537204</v>
-      </c>
-      <c r="H8" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8908006537204</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -688,8 +711,10 @@
       <c r="C9" t="n">
         <v>339</v>
       </c>
-      <c r="D9" t="n">
-        <v>95030020</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E9" t="n">
         <v>0.05</v>
@@ -699,12 +724,13 @@
           <t>SMRT1022</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>8908006537211</v>
-      </c>
-      <c r="H9" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8908006537211</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -718,8 +744,10 @@
       <c r="C10" t="n">
         <v>339</v>
       </c>
-      <c r="D10" t="n">
-        <v>95030020</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E10" t="n">
         <v>0.05</v>
@@ -729,12 +757,13 @@
           <t>SMRT1023</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>8908006537228</v>
-      </c>
-      <c r="H10" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8908006537228</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -748,8 +777,10 @@
       <c r="C11" t="n">
         <v>339</v>
       </c>
-      <c r="D11" t="n">
-        <v>95030020</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E11" t="n">
         <v>0.05</v>
@@ -759,12 +790,13 @@
           <t>SMRT1024</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>8908006537235</v>
-      </c>
-      <c r="H11" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8908006537235</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -778,8 +810,10 @@
       <c r="C12" t="n">
         <v>339</v>
       </c>
-      <c r="D12" t="n">
-        <v>95030020</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E12" t="n">
         <v>0.05</v>
@@ -789,12 +823,13 @@
           <t>SMRT1025</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>8908006537242</v>
-      </c>
-      <c r="H12" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8908006537242</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -808,8 +843,10 @@
       <c r="C13" t="n">
         <v>339</v>
       </c>
-      <c r="D13" t="n">
-        <v>95030020</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E13" t="n">
         <v>0.05</v>
@@ -819,12 +856,13 @@
           <t>SMRT1026</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>8908006537259</v>
-      </c>
-      <c r="H13" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8908006537259</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -838,8 +876,10 @@
       <c r="C14" t="n">
         <v>729</v>
       </c>
-      <c r="D14" t="n">
-        <v>95030020</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E14" t="n">
         <v>0.05</v>
@@ -849,12 +889,13 @@
           <t>SMRT1027</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>8908006537266</v>
-      </c>
-      <c r="H14" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8908006537266</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -868,8 +909,10 @@
       <c r="C15" t="n">
         <v>1159</v>
       </c>
-      <c r="D15" t="n">
-        <v>95030020</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E15" t="n">
         <v>0.05</v>
@@ -879,12 +922,13 @@
           <t>SMRT1028</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>8908006537273</v>
-      </c>
-      <c r="H15" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8908006537273</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -898,8 +942,10 @@
       <c r="C16" t="n">
         <v>1059</v>
       </c>
-      <c r="D16" t="n">
-        <v>95030020</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E16" t="n">
         <v>0.05</v>
@@ -909,12 +955,13 @@
           <t>SMRT1031</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>8908006537303</v>
-      </c>
-      <c r="H16" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>8908006537303</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -928,8 +975,10 @@
       <c r="C17" t="n">
         <v>1399</v>
       </c>
-      <c r="D17" t="n">
-        <v>95030020</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E17" t="n">
         <v>0.05</v>
@@ -939,14 +988,17 @@
           <t>SMRT1032</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>8908006537310</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8908006537310</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>8606924</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -960,8 +1012,10 @@
       <c r="C18" t="n">
         <v>339</v>
       </c>
-      <c r="D18" t="n">
-        <v>95030020</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E18" t="n">
         <v>0.05</v>
@@ -971,12 +1025,13 @@
           <t>SMRT1033</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>8908006537327</v>
-      </c>
-      <c r="H18" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8908006537327</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -990,8 +1045,10 @@
       <c r="C19" t="n">
         <v>339</v>
       </c>
-      <c r="D19" t="n">
-        <v>95030020</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E19" t="n">
         <v>0.05</v>
@@ -1001,12 +1058,13 @@
           <t>SMRT1034</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>8908006537334</v>
-      </c>
-      <c r="H19" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>8908006537334</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1020,8 +1078,10 @@
       <c r="C20" t="n">
         <v>339</v>
       </c>
-      <c r="D20" t="n">
-        <v>95030020</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E20" t="n">
         <v>0.05</v>
@@ -1031,12 +1091,13 @@
           <t>SMRT1035</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>8908006537341</v>
-      </c>
-      <c r="H20" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>8908006537341</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1050,8 +1111,10 @@
       <c r="C21" t="n">
         <v>2229</v>
       </c>
-      <c r="D21" t="n">
-        <v>95030020</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E21" t="n">
         <v>0.05</v>
@@ -1061,12 +1124,13 @@
           <t>SMRT1037</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>8908006537365</v>
-      </c>
-      <c r="H21" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8908006537365</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1080,8 +1144,10 @@
       <c r="C22" t="n">
         <v>849</v>
       </c>
-      <c r="D22" t="n">
-        <v>95030020</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E22" t="n">
         <v>0.05</v>
@@ -1091,14 +1157,16 @@
           <t>SMRT1040</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>8908006537396</v>
-      </c>
-      <c r="H22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I22" t="n">
-        <v>61820</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>8908006537396</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>61820</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1113,8 +1181,10 @@
       <c r="C23" t="n">
         <v>869</v>
       </c>
-      <c r="D23" t="n">
-        <v>95030020</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E23" t="n">
         <v>0.05</v>
@@ -1124,12 +1194,13 @@
           <t>SMRT1042</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>8908006537419</v>
-      </c>
-      <c r="H23" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>8908006537419</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1143,8 +1214,10 @@
       <c r="C24" t="n">
         <v>339</v>
       </c>
-      <c r="D24" t="n">
-        <v>95030020</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E24" t="n">
         <v>0.05</v>
@@ -1154,12 +1227,13 @@
           <t>SMRT1043</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>8908006537426</v>
-      </c>
-      <c r="H24" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>8908006537426</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1173,8 +1247,10 @@
       <c r="C25" t="n">
         <v>339</v>
       </c>
-      <c r="D25" t="n">
-        <v>95030020</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E25" t="n">
         <v>0.05</v>
@@ -1184,12 +1260,13 @@
           <t>SMRT1044</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>8908006537433</v>
-      </c>
-      <c r="H25" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>8908006537433</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1203,8 +1280,10 @@
       <c r="C26" t="n">
         <v>339</v>
       </c>
-      <c r="D26" t="n">
-        <v>95030020</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E26" t="n">
         <v>0.05</v>
@@ -1214,12 +1293,13 @@
           <t>SMRT1045</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>8908006537440</v>
-      </c>
-      <c r="H26" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>8908006537440</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1233,8 +1313,10 @@
       <c r="C27" t="n">
         <v>339</v>
       </c>
-      <c r="D27" t="n">
-        <v>95030020</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E27" t="n">
         <v>0.05</v>
@@ -1244,12 +1326,13 @@
           <t>SMRT1046</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>8908006537457</v>
-      </c>
-      <c r="H27" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>8908006537457</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1263,8 +1346,10 @@
       <c r="C28" t="n">
         <v>339</v>
       </c>
-      <c r="D28" t="n">
-        <v>95030020</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E28" t="n">
         <v>0.05</v>
@@ -1274,12 +1359,13 @@
           <t>SMRT1047</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>8908006537464</v>
-      </c>
-      <c r="H28" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>8908006537464</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1293,8 +1379,10 @@
       <c r="C29" t="n">
         <v>769</v>
       </c>
-      <c r="D29" t="n">
-        <v>95030020</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E29" t="n">
         <v>0.05</v>
@@ -1304,14 +1392,16 @@
           <t>SMRT1048</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>8908006537471</v>
-      </c>
-      <c r="H29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I29" t="n">
-        <v>64139</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>8908006537471</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>64139</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1326,8 +1416,10 @@
       <c r="C30" t="n">
         <v>679</v>
       </c>
-      <c r="D30" t="n">
-        <v>95030020</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E30" t="n">
         <v>0.05</v>
@@ -1337,12 +1429,13 @@
           <t>SMRT1049</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>8908006537488</v>
-      </c>
-      <c r="H30" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>8908006537488</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1356,8 +1449,10 @@
       <c r="C31" t="n">
         <v>679</v>
       </c>
-      <c r="D31" t="n">
-        <v>95030020</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E31" t="n">
         <v>0.05</v>
@@ -1367,12 +1462,13 @@
           <t>SMRT1050</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>8908006537501</v>
-      </c>
-      <c r="H31" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>8908006537501</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1386,8 +1482,10 @@
       <c r="C32" t="n">
         <v>1059</v>
       </c>
-      <c r="D32" t="n">
-        <v>95030020</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E32" t="n">
         <v>0.05</v>
@@ -1397,12 +1495,13 @@
           <t>SMRT1055</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>8908006537556</v>
-      </c>
-      <c r="H32" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>8908006537556</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1416,8 +1515,10 @@
       <c r="C33" t="n">
         <v>1899</v>
       </c>
-      <c r="D33" t="n">
-        <v>95030010</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>95030010</t>
+        </is>
       </c>
       <c r="E33" t="n">
         <v>0.18</v>
@@ -1427,12 +1528,13 @@
           <t>SMRT1057</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>8908006537570</v>
-      </c>
-      <c r="H33" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>8908006537570</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1446,8 +1548,10 @@
       <c r="C34" t="n">
         <v>4999</v>
       </c>
-      <c r="D34" t="n">
-        <v>95030010</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>95030010</t>
+        </is>
       </c>
       <c r="E34" t="n">
         <v>0.18</v>
@@ -1457,12 +1561,13 @@
           <t>SMRT1068</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>8908006537631</v>
-      </c>
-      <c r="H34" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>8908006537631</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1476,8 +1581,10 @@
       <c r="C35" t="n">
         <v>1159</v>
       </c>
-      <c r="D35" t="n">
-        <v>95030020</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E35" t="n">
         <v>0.05</v>
@@ -1487,12 +1594,13 @@
           <t>SMRT1076</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>8908006537716</v>
-      </c>
-      <c r="H35" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>8908006537716</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1506,8 +1614,10 @@
       <c r="C36" t="n">
         <v>1159</v>
       </c>
-      <c r="D36" t="n">
-        <v>95030020</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E36" t="n">
         <v>0.05</v>
@@ -1517,12 +1627,13 @@
           <t>SMRT1077</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>8908006537723</v>
-      </c>
-      <c r="H36" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>8908006537723</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1536,8 +1647,10 @@
       <c r="C37" t="n">
         <v>969</v>
       </c>
-      <c r="D37" t="n">
-        <v>95030020</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E37" t="n">
         <v>0.05</v>
@@ -1547,12 +1660,13 @@
           <t>SMRT1078</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>8908006537730</v>
-      </c>
-      <c r="H37" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>8908006537730</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1566,8 +1680,10 @@
       <c r="C38" t="n">
         <v>159</v>
       </c>
-      <c r="D38" t="n">
-        <v>95030020</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E38" t="n">
         <v>0.05</v>
@@ -1577,12 +1693,13 @@
           <t>SMRT1082</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>8908006537778</v>
-      </c>
-      <c r="H38" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>8908006537778</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1596,8 +1713,10 @@
       <c r="C39" t="n">
         <v>159</v>
       </c>
-      <c r="D39" t="n">
-        <v>95030020</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E39" t="n">
         <v>0.05</v>
@@ -1607,12 +1726,13 @@
           <t>SMRT1083</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>8908006537785</v>
-      </c>
-      <c r="H39" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>8908006537785</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1626,8 +1746,10 @@
       <c r="C40" t="n">
         <v>159</v>
       </c>
-      <c r="D40" t="n">
-        <v>95030020</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E40" t="n">
         <v>0.05</v>
@@ -1637,12 +1759,13 @@
           <t>SMRT1084</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>8908006537792</v>
-      </c>
-      <c r="H40" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>8908006537792</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1656,8 +1779,10 @@
       <c r="C41" t="n">
         <v>159</v>
       </c>
-      <c r="D41" t="n">
-        <v>95030020</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E41" t="n">
         <v>0.05</v>
@@ -1667,12 +1792,13 @@
           <t>SMRT1085</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>8908006537808</v>
-      </c>
-      <c r="H41" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>8908006537808</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1686,8 +1812,10 @@
       <c r="C42" t="n">
         <v>159</v>
       </c>
-      <c r="D42" t="n">
-        <v>95030020</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E42" t="n">
         <v>0.05</v>
@@ -1697,12 +1825,13 @@
           <t>SMRT1086</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>8908006537815</v>
-      </c>
-      <c r="H42" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>8908006537815</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1716,8 +1845,10 @@
       <c r="C43" t="n">
         <v>159</v>
       </c>
-      <c r="D43" t="n">
-        <v>95030020</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E43" t="n">
         <v>0.05</v>
@@ -1727,12 +1858,13 @@
           <t>SMRT1087</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>8908006537822</v>
-      </c>
-      <c r="H43" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>8908006537822</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1746,8 +1878,10 @@
       <c r="C44" t="n">
         <v>629</v>
       </c>
-      <c r="D44" t="n">
-        <v>95030020</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E44" t="n">
         <v>0.05</v>
@@ -1757,12 +1891,13 @@
           <t>SMRT1090</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>8908006537853</v>
-      </c>
-      <c r="H44" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>8908006537853</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1776,8 +1911,10 @@
       <c r="C45" t="n">
         <v>159</v>
       </c>
-      <c r="D45" t="n">
-        <v>95030020</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E45" t="n">
         <v>0.05</v>
@@ -1787,12 +1924,13 @@
           <t>SMRT1091</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>8908006537860</v>
-      </c>
-      <c r="H45" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8908006537860</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1806,8 +1944,10 @@
       <c r="C46" t="n">
         <v>159</v>
       </c>
-      <c r="D46" t="n">
-        <v>95030020</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E46" t="n">
         <v>0.05</v>
@@ -1817,12 +1957,13 @@
           <t>SMRT1092</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>8908006537877</v>
-      </c>
-      <c r="H46" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>8908006537877</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1836,8 +1977,10 @@
       <c r="C47" t="n">
         <v>159</v>
       </c>
-      <c r="D47" t="n">
-        <v>95030020</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E47" t="n">
         <v>0.05</v>
@@ -1847,12 +1990,13 @@
           <t>SMRT1093</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>8908006537884</v>
-      </c>
-      <c r="H47" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>8908006537884</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1866,8 +2010,10 @@
       <c r="C48" t="n">
         <v>529</v>
       </c>
-      <c r="D48" t="n">
-        <v>95030020</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E48" t="n">
         <v>0.05</v>
@@ -1877,14 +2023,17 @@
           <t>SMRT1098</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>8908006537907</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>8908006537907</t>
+        </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>8606931</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1898,8 +2047,10 @@
       <c r="C49" t="n">
         <v>869</v>
       </c>
-      <c r="D49" t="n">
-        <v>95030020</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E49" t="n">
         <v>0.05</v>
@@ -1909,12 +2060,13 @@
           <t>SMRT1099</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>8908006537914</v>
-      </c>
-      <c r="H49" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>8908006537914</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1928,8 +2080,10 @@
       <c r="C50" t="n">
         <v>1059</v>
       </c>
-      <c r="D50" t="n">
-        <v>95030020</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E50" t="n">
         <v>0.05</v>
@@ -1939,12 +2093,13 @@
           <t>SMRT1101</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>8908006537921</v>
-      </c>
-      <c r="H50" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>8908006537921</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1958,8 +2113,10 @@
       <c r="C51" t="n">
         <v>379</v>
       </c>
-      <c r="D51" t="n">
-        <v>95030020</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E51" t="n">
         <v>0.05</v>
@@ -1969,12 +2126,13 @@
           <t>SMRT1107</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>8908006537983</v>
-      </c>
-      <c r="H51" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>8908006537983</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1988,8 +2146,10 @@
       <c r="C52" t="n">
         <v>379</v>
       </c>
-      <c r="D52" t="n">
-        <v>95030020</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E52" t="n">
         <v>0.05</v>
@@ -1999,12 +2159,13 @@
           <t>SMRT1108</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>8908006537990</v>
-      </c>
-      <c r="H52" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>8908006537990</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2018,8 +2179,10 @@
       <c r="C53" t="n">
         <v>549</v>
       </c>
-      <c r="D53" t="n">
-        <v>95030020</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E53" t="n">
         <v>0.05</v>
@@ -2029,16 +2192,20 @@
           <t>SMRT1109(V6)</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>8908006537297</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>8908006537297</t>
+        </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>8606935</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>91537</v>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>91537</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -2053,8 +2220,10 @@
       <c r="C54" t="n">
         <v>379</v>
       </c>
-      <c r="D54" t="n">
-        <v>95030020</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E54" t="n">
         <v>0.05</v>
@@ -2064,12 +2233,13 @@
           <t>SMRT1110</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>8908006537389</v>
-      </c>
-      <c r="H54" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>8908006537389</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2083,8 +2253,10 @@
       <c r="C55" t="n">
         <v>629</v>
       </c>
-      <c r="D55" t="n">
-        <v>95030020</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E55" t="n">
         <v>0.05</v>
@@ -2094,12 +2266,13 @@
           <t>SMRT1112</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>8908006537549</v>
-      </c>
-      <c r="H55" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>8908006537549</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2113,8 +2286,10 @@
       <c r="C56" t="n">
         <v>1159</v>
       </c>
-      <c r="D56" t="n">
-        <v>95030020</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E56" t="n">
         <v>0.05</v>
@@ -2124,12 +2299,13 @@
           <t>SMRT1113</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>8908006537372</v>
-      </c>
-      <c r="H56" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>8908006537372</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2143,8 +2319,10 @@
       <c r="C57" t="n">
         <v>1259</v>
       </c>
-      <c r="D57" t="n">
-        <v>95030020</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E57" t="n">
         <v>0.05</v>
@@ -2154,12 +2332,13 @@
           <t>SMRT1117</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>8908006537969</v>
-      </c>
-      <c r="H57" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>8908006537969</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2173,8 +2352,10 @@
       <c r="C58" t="n">
         <v>1159</v>
       </c>
-      <c r="D58" t="n">
-        <v>95030020</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E58" t="n">
         <v>0.05</v>
@@ -2184,12 +2365,13 @@
           <t>SMRT1118</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>8908006537976</v>
-      </c>
-      <c r="H58" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>8908006537976</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2203,8 +2385,10 @@
       <c r="C59" t="n">
         <v>1159</v>
       </c>
-      <c r="D59" t="n">
-        <v>95030020</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E59" t="n">
         <v>0.05</v>
@@ -2214,12 +2398,13 @@
           <t>SMRT1124</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>8908011797020</v>
-      </c>
-      <c r="H59" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>8908011797020</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2233,8 +2418,10 @@
       <c r="C60" t="n">
         <v>1159</v>
       </c>
-      <c r="D60" t="n">
-        <v>95030020</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E60" t="n">
         <v>0.05</v>
@@ -2244,12 +2431,13 @@
           <t>SMRT1125</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>8908011797037</v>
-      </c>
-      <c r="H60" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>8908011797037</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2263,8 +2451,10 @@
       <c r="C61" t="n">
         <v>629</v>
       </c>
-      <c r="D61" t="n">
-        <v>95030020</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E61" t="n">
         <v>0.05</v>
@@ -2274,12 +2464,13 @@
           <t>SMRT1128</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>8908011797051</v>
-      </c>
-      <c r="H61" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>8908011797051</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2293,8 +2484,10 @@
       <c r="C62" t="n">
         <v>869</v>
       </c>
-      <c r="D62" t="n">
-        <v>95030020</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E62" t="n">
         <v>0.05</v>
@@ -2304,12 +2497,13 @@
           <t>SMRT1130</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>8908011797075</v>
-      </c>
-      <c r="H62" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>8908011797075</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2323,8 +2517,10 @@
       <c r="C63" t="n">
         <v>1259</v>
       </c>
-      <c r="D63" t="n">
-        <v>95030020</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E63" t="n">
         <v>0.05</v>
@@ -2334,12 +2530,13 @@
           <t>SMRT1131</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>8908011797068</v>
-      </c>
-      <c r="H63" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>8908011797068</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2353,8 +2550,10 @@
       <c r="C64" t="n">
         <v>1999</v>
       </c>
-      <c r="D64" t="n">
-        <v>95030010</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>95030010</t>
+        </is>
       </c>
       <c r="E64" t="n">
         <v>0.18</v>
@@ -2364,12 +2563,13 @@
           <t>SMRT1132</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>8908011797136</v>
-      </c>
-      <c r="H64" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>8908011797136</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2383,8 +2583,10 @@
       <c r="C65" t="n">
         <v>1059</v>
       </c>
-      <c r="D65" t="n">
-        <v>95030020</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E65" t="n">
         <v>0.05</v>
@@ -2394,12 +2596,13 @@
           <t>SMRT1134</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>8908011797082</v>
-      </c>
-      <c r="H65" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>8908011797082</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2413,8 +2616,10 @@
       <c r="C66" t="n">
         <v>1249</v>
       </c>
-      <c r="D66" t="n">
-        <v>95030020</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E66" t="n">
         <v>0.05</v>
@@ -2424,16 +2629,20 @@
           <t>SMRT1135</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>8908011797099</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>8908011797099</t>
+        </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>8606950</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>51344</v>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>51344</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -2448,8 +2657,10 @@
       <c r="C67" t="n">
         <v>1259</v>
       </c>
-      <c r="D67" t="n">
-        <v>95030010</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>95030010</t>
+        </is>
       </c>
       <c r="E67" t="n">
         <v>0.18</v>
@@ -2459,16 +2670,20 @@
           <t>SMRT1139-18</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>8908011797105</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>8908011797105</t>
+        </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>8606952</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>56867</v>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>56867</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -2483,8 +2698,10 @@
       <c r="C68" t="n">
         <v>979</v>
       </c>
-      <c r="D68" t="n">
-        <v>95030020</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E68" t="n">
         <v>0.05</v>
@@ -2494,16 +2711,20 @@
           <t>SMRT1163(V3)</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>8908011797143</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>8908011797143</t>
+        </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>8947269</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>73783</v>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>73783</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -2518,8 +2739,10 @@
       <c r="C69" t="n">
         <v>1549</v>
       </c>
-      <c r="D69" t="n">
-        <v>95030020</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E69" t="n">
         <v>0.05</v>
@@ -2529,14 +2752,17 @@
           <t>SMRT1165</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>8908011797150</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>8908011797150</t>
+        </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>8947250</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2550,8 +2776,10 @@
       <c r="C70" t="n">
         <v>3879</v>
       </c>
-      <c r="D70" t="n">
-        <v>95030020</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E70" t="n">
         <v>0.05</v>
@@ -2561,12 +2789,13 @@
           <t>SMRT1168</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>8908011797129</v>
-      </c>
-      <c r="H70" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>8908011797129</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2580,8 +2809,10 @@
       <c r="C71" t="n">
         <v>1599</v>
       </c>
-      <c r="D71" t="n">
-        <v>95030020</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E71" t="n">
         <v>0.05</v>
@@ -2591,16 +2822,20 @@
           <t>SMRT1169</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>8908011797204</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>8908011797204</t>
+        </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>8947251</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>93878</v>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>93878</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -2615,8 +2850,10 @@
       <c r="C72" t="n">
         <v>849</v>
       </c>
-      <c r="D72" t="n">
-        <v>95030020</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E72" t="n">
         <v>0.05</v>
@@ -2626,16 +2863,20 @@
           <t>SMRT1174</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>8908011797211</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>8908011797211</t>
+        </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>8947249</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>97450</v>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>97450</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -2650,8 +2891,10 @@
       <c r="C73" t="n">
         <v>669</v>
       </c>
-      <c r="D73" t="n">
-        <v>95030020</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E73" t="n">
         <v>0.05</v>
@@ -2661,12 +2904,13 @@
           <t>SMRT1175</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>8908011797167</v>
-      </c>
-      <c r="H73" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>8908011797167</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2680,8 +2924,10 @@
       <c r="C74" t="n">
         <v>669</v>
       </c>
-      <c r="D74" t="n">
-        <v>95030020</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E74" t="n">
         <v>0.05</v>
@@ -2691,12 +2937,13 @@
           <t>SMRT1176</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>8908011797174</v>
-      </c>
-      <c r="H74" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>8908011797174</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2710,8 +2957,10 @@
       <c r="C75" t="n">
         <v>669</v>
       </c>
-      <c r="D75" t="n">
-        <v>95030020</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E75" t="n">
         <v>0.05</v>
@@ -2721,12 +2970,13 @@
           <t>SMRT1177</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>8908011797181</v>
-      </c>
-      <c r="H75" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>8908011797181</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2740,8 +2990,10 @@
       <c r="C76" t="n">
         <v>669</v>
       </c>
-      <c r="D76" t="n">
-        <v>95030020</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E76" t="n">
         <v>0.05</v>
@@ -2751,12 +3003,13 @@
           <t>SMRT1178</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>8908011797198</v>
-      </c>
-      <c r="H76" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>8908011797198</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2770,8 +3023,10 @@
       <c r="C77" t="n">
         <v>1099</v>
       </c>
-      <c r="D77" t="n">
-        <v>95030020</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E77" t="n">
         <v>0.05</v>
@@ -2781,16 +3036,20 @@
           <t>SMRT1179</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>8908011797228</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>8908011797228</t>
+        </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>13353538</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>75870</v>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>75870</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -2805,8 +3064,10 @@
       <c r="C78" t="n">
         <v>769</v>
       </c>
-      <c r="D78" t="n">
-        <v>95030020</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E78" t="n">
         <v>0.05</v>
@@ -2816,12 +3077,13 @@
           <t>SMRT1180</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>8908011797242</v>
-      </c>
-      <c r="H78" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>8908011797242</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2835,8 +3097,10 @@
       <c r="C79" t="n">
         <v>819</v>
       </c>
-      <c r="D79" t="n">
-        <v>95030020</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E79" t="n">
         <v>0.05</v>
@@ -2846,12 +3110,13 @@
           <t>SMRT1181</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>8908011797273</v>
-      </c>
-      <c r="H79" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>8908011797273</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2865,8 +3130,10 @@
       <c r="C80" t="n">
         <v>1299</v>
       </c>
-      <c r="D80" t="n">
-        <v>95030020</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E80" t="n">
         <v>0.05</v>
@@ -2876,16 +3143,20 @@
           <t>SMRT1182</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>8908011797297</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>8908011797297</t>
+        </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>10127435</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>85666</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>85666</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -2900,8 +3171,10 @@
       <c r="C81" t="n">
         <v>919</v>
       </c>
-      <c r="D81" t="n">
-        <v>95030020</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E81" t="n">
         <v>0.05</v>
@@ -2911,12 +3184,13 @@
           <t>SMRT1183</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>8908011797280</v>
-      </c>
-      <c r="H81" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>8908011797280</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2930,8 +3204,10 @@
       <c r="C82" t="n">
         <v>1159</v>
       </c>
-      <c r="D82" t="n">
-        <v>95030020</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E82" t="n">
         <v>0.05</v>
@@ -2941,16 +3217,20 @@
           <t>SMRT1184</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>8908011797327</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>8908011797327</t>
+        </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>13353535</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>65810</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>65810</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -2965,8 +3245,10 @@
       <c r="C83" t="n">
         <v>869</v>
       </c>
-      <c r="D83" t="n">
-        <v>95030020</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E83" t="n">
         <v>0.05</v>
@@ -2976,12 +3258,13 @@
           <t>SMRT1186</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>8908011797235</v>
-      </c>
-      <c r="H83" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>8908011797235</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2995,8 +3278,10 @@
       <c r="C84" t="n">
         <v>819</v>
       </c>
-      <c r="D84" t="n">
-        <v>95030020</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E84" t="n">
         <v>0.05</v>
@@ -3006,12 +3291,13 @@
           <t>SMRT1187</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>8908011797266</v>
-      </c>
-      <c r="H84" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>8908011797266</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3025,8 +3311,10 @@
       <c r="C85" t="n">
         <v>868</v>
       </c>
-      <c r="D85" t="n">
-        <v>95030020</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E85" t="n">
         <v>0.05</v>
@@ -3036,12 +3324,13 @@
           <t>SMRT1188</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>8908011797310</v>
-      </c>
-      <c r="H85" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>8908011797310</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3055,8 +3344,10 @@
       <c r="C86" t="n">
         <v>869</v>
       </c>
-      <c r="D86" t="n">
-        <v>95030020</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E86" t="n">
         <v>0.05</v>
@@ -3066,12 +3357,13 @@
           <t>SMRT1189</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>8908011797334</v>
-      </c>
-      <c r="H86" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>8908011797334</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3085,8 +3377,10 @@
       <c r="C87" t="n">
         <v>1059</v>
       </c>
-      <c r="D87" t="n">
-        <v>95030020</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E87" t="n">
         <v>0.05</v>
@@ -3096,12 +3390,13 @@
           <t>SMRT1190</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>8908011797426</v>
-      </c>
-      <c r="H87" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>8908011797426</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3115,8 +3410,10 @@
       <c r="C88" t="n">
         <v>869</v>
       </c>
-      <c r="D88" t="n">
-        <v>95030020</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E88" t="n">
         <v>0.05</v>
@@ -3126,16 +3423,20 @@
           <t>SMRT1191</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>8908006537563</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>8908006537563</t>
+        </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>10712380</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>74823</v>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>74823</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -3150,8 +3451,10 @@
       <c r="C89" t="n">
         <v>1099</v>
       </c>
-      <c r="D89" t="n">
-        <v>95030020</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E89" t="n">
         <v>0.05</v>
@@ -3161,16 +3464,20 @@
           <t>SMRT1192</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>8908011797303</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>8908011797303</t>
+        </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>10127433</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>79024</v>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>79024</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -3185,8 +3492,10 @@
       <c r="C90" t="n">
         <v>1059</v>
       </c>
-      <c r="D90" t="n">
-        <v>95030020</v>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E90" t="n">
         <v>0.05</v>
@@ -3196,12 +3505,13 @@
           <t>SMRT1197</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>8908006537587</v>
-      </c>
-      <c r="H90" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>8908006537587</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3215,8 +3525,10 @@
       <c r="C91" t="n">
         <v>869</v>
       </c>
-      <c r="D91" t="n">
-        <v>95030020</v>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E91" t="n">
         <v>0.05</v>
@@ -3226,12 +3538,13 @@
           <t>SMRT1204</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>8908006537594</v>
-      </c>
-      <c r="H91" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>8908006537594</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3245,8 +3558,10 @@
       <c r="C92" t="n">
         <v>869</v>
       </c>
-      <c r="D92" t="n">
-        <v>95030020</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E92" t="n">
         <v>0.05</v>
@@ -3256,12 +3571,13 @@
           <t>SMRT1206</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>8908006537709</v>
-      </c>
-      <c r="H92" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>8908006537709</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3275,8 +3591,10 @@
       <c r="C93" t="n">
         <v>819</v>
       </c>
-      <c r="D93" t="n">
-        <v>95030020</v>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E93" t="n">
         <v>0.05</v>
@@ -3286,12 +3604,13 @@
           <t>SMRT1209</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>8908011797471</v>
-      </c>
-      <c r="H93" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>8908011797471</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3305,8 +3624,10 @@
       <c r="C94" t="n">
         <v>1099</v>
       </c>
-      <c r="D94" t="n">
-        <v>95030010</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>95030010</t>
+        </is>
       </c>
       <c r="E94" t="n">
         <v>0.18</v>
@@ -3316,16 +3637,20 @@
           <t>SMRT1214-18</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>8908011797488</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>8908011797488</t>
+        </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>13353534</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>70537</v>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>70537</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -3340,8 +3665,10 @@
       <c r="C95" t="n">
         <v>1059</v>
       </c>
-      <c r="D95" t="n">
-        <v>95030020</v>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E95" t="n">
         <v>0.05</v>
@@ -3351,14 +3678,16 @@
           <t>SMRT1215(V2)</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>8908011797464</v>
-      </c>
-      <c r="H95" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I95" t="n">
-        <v>481367</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>8908011797464</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>481367</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -3373,8 +3702,10 @@
       <c r="C96" t="n">
         <v>1399</v>
       </c>
-      <c r="D96" t="n">
-        <v>95030010</v>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>95030010</t>
+        </is>
       </c>
       <c r="E96" t="n">
         <v>0.18</v>
@@ -3384,16 +3715,20 @@
           <t>SMRT1216</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>8908011797518</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>8908011797518</t>
+        </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>13353529</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>86497</v>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>86497</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -3408,8 +3743,10 @@
       <c r="C97" t="n">
         <v>819</v>
       </c>
-      <c r="D97" t="n">
-        <v>95030020</v>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E97" t="n">
         <v>0.05</v>
@@ -3419,12 +3756,13 @@
           <t>SMRT1220</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>8908011797570</v>
-      </c>
-      <c r="H97" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>8908011797570</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3438,8 +3776,10 @@
       <c r="C98" t="n">
         <v>1159</v>
       </c>
-      <c r="D98" t="n">
-        <v>95030020</v>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E98" t="n">
         <v>0.05</v>
@@ -3449,12 +3789,13 @@
           <t>SMRT1221(V2)</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>8908011797792</v>
-      </c>
-      <c r="H98" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>8908011797792</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3468,8 +3809,10 @@
       <c r="C99" t="n">
         <v>969</v>
       </c>
-      <c r="D99" t="n">
-        <v>95030020</v>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E99" t="n">
         <v>0.05</v>
@@ -3479,16 +3822,20 @@
           <t>SMRT1222</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>8908011797549</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>8908011797549</t>
+        </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>13353532</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>96340</v>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>96340</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -3503,8 +3850,10 @@
       <c r="C100" t="n">
         <v>869</v>
       </c>
-      <c r="D100" t="n">
-        <v>95030020</v>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E100" t="n">
         <v>0.05</v>
@@ -3514,12 +3863,13 @@
           <t>SMRT1223</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>8908011797532</v>
-      </c>
-      <c r="H100" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>8908011797532</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3533,8 +3883,10 @@
       <c r="C101" t="n">
         <v>969</v>
       </c>
-      <c r="D101" t="n">
-        <v>95030020</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E101" t="n">
         <v>0.05</v>
@@ -3544,12 +3896,13 @@
           <t>SMRT1226</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>8908011797563</v>
-      </c>
-      <c r="H101" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>8908011797563</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3563,8 +3916,10 @@
       <c r="C102" t="n">
         <v>1739</v>
       </c>
-      <c r="D102" t="n">
-        <v>95030020</v>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E102" t="n">
         <v>0.05</v>
@@ -3574,12 +3929,13 @@
           <t>SMRT1227</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>8908011797556</v>
-      </c>
-      <c r="H102" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>8908011797556</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3593,8 +3949,10 @@
       <c r="C103" t="n">
         <v>869</v>
       </c>
-      <c r="D103" t="n">
-        <v>95030020</v>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E103" t="n">
         <v>0.05</v>
@@ -3604,12 +3962,13 @@
           <t>SMRT1228</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>8908011797587</v>
-      </c>
-      <c r="H103" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>8908011797587</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3623,8 +3982,10 @@
       <c r="C104" t="n">
         <v>1099</v>
       </c>
-      <c r="D104" t="n">
-        <v>95030010</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>95030010</t>
+        </is>
       </c>
       <c r="E104" t="n">
         <v>0.18</v>
@@ -3634,16 +3995,20 @@
           <t>SMRT1230-18</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>8908011797600</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>8908011797600</t>
+        </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>13694135</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>73466</v>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>73466</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -3658,8 +4023,10 @@
       <c r="C105" t="n">
         <v>1299</v>
       </c>
-      <c r="D105" t="n">
-        <v>95030020</v>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E105" t="n">
         <v>0.05</v>
@@ -3669,12 +4036,13 @@
           <t>SMRT1233</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>8908011797617</v>
-      </c>
-      <c r="H105" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>8908011797617</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3688,8 +4056,10 @@
       <c r="C106" t="n">
         <v>999</v>
       </c>
-      <c r="D106" t="n">
-        <v>95030020</v>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E106" t="n">
         <v>0.05</v>
@@ -3699,14 +4069,16 @@
           <t>SMRT1236</t>
         </is>
       </c>
-      <c r="G106" t="n">
-        <v>8908011797648</v>
-      </c>
-      <c r="H106" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I106" t="n">
-        <v>458614</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>8908011797648</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>458614</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -3721,8 +4093,10 @@
       <c r="C107" t="n">
         <v>1099</v>
       </c>
-      <c r="D107" t="n">
-        <v>95030020</v>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E107" t="n">
         <v>0.05</v>
@@ -3732,14 +4106,17 @@
           <t>SMRT1238</t>
         </is>
       </c>
-      <c r="G107" t="n">
-        <v>8908011797655</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>8908011797655</t>
+        </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>14626588</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3753,8 +4130,10 @@
       <c r="C108" t="n">
         <v>869</v>
       </c>
-      <c r="D108" t="n">
-        <v>95030020</v>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E108" t="n">
         <v>0.05</v>
@@ -3764,12 +4143,13 @@
           <t>SMRT1240</t>
         </is>
       </c>
-      <c r="G108" t="n">
-        <v>8908011797624</v>
-      </c>
-      <c r="H108" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>8908011797624</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3783,8 +4163,10 @@
       <c r="C109" t="n">
         <v>969</v>
       </c>
-      <c r="D109" t="n">
-        <v>95030020</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E109" t="n">
         <v>0.05</v>
@@ -3794,14 +4176,17 @@
           <t>SMRT1241</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>8908011797747</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>8908011797747</t>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>17856011</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3815,8 +4200,10 @@
       <c r="C110" t="n">
         <v>819</v>
       </c>
-      <c r="D110" t="n">
-        <v>95030020</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E110" t="n">
         <v>0.05</v>
@@ -3826,16 +4213,20 @@
           <t>SMRT1242V2</t>
         </is>
       </c>
-      <c r="G110" t="n">
-        <v>8908011797679</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>8908011797679</t>
+        </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>15433823</t>
         </is>
       </c>
-      <c r="I110" t="n">
-        <v>480751</v>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>480751</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -3850,8 +4241,10 @@
       <c r="C111" t="n">
         <v>899</v>
       </c>
-      <c r="D111" t="n">
-        <v>95030020</v>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E111" t="n">
         <v>0.05</v>
@@ -3861,12 +4254,13 @@
           <t>SMRT1244</t>
         </is>
       </c>
-      <c r="G111" t="n">
-        <v>8908011797662</v>
-      </c>
-      <c r="H111" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>8908011797662</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3880,8 +4274,10 @@
       <c r="C112" t="n">
         <v>1699</v>
       </c>
-      <c r="D112" t="n">
-        <v>95030010</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>95030010</t>
+        </is>
       </c>
       <c r="E112" t="n">
         <v>0.18</v>
@@ -3891,16 +4287,20 @@
           <t>SMRT1245</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>8908011797860</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>8908011797860</t>
+        </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>19825872</t>
         </is>
       </c>
-      <c r="I112" t="n">
-        <v>158421</v>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>158421</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -3915,8 +4315,10 @@
       <c r="C113" t="n">
         <v>919</v>
       </c>
-      <c r="D113" t="n">
-        <v>95030020</v>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E113" t="n">
         <v>0.05</v>
@@ -3926,12 +4328,13 @@
           <t>SMRT1246</t>
         </is>
       </c>
-      <c r="G113" t="n">
-        <v>8908011797723</v>
-      </c>
-      <c r="H113" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>8908011797723</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3945,8 +4348,10 @@
       <c r="C114" t="n">
         <v>769</v>
       </c>
-      <c r="D114" t="n">
-        <v>95030020</v>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E114" t="n">
         <v>0.05</v>
@@ -3956,16 +4361,20 @@
           <t>SMRT1253</t>
         </is>
       </c>
-      <c r="G114" t="n">
-        <v>8908011797693</v>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>8908011797693</t>
+        </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>17856008</t>
         </is>
       </c>
-      <c r="I114" t="n">
-        <v>523050</v>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>523050</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -3980,8 +4389,10 @@
       <c r="C115" t="n">
         <v>629</v>
       </c>
-      <c r="D115" t="n">
-        <v>95030020</v>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E115" t="n">
         <v>0.05</v>
@@ -3991,12 +4402,13 @@
           <t>SMRT1254</t>
         </is>
       </c>
-      <c r="G115" t="n">
-        <v>8908011797709</v>
-      </c>
-      <c r="H115" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>8908011797709</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4010,8 +4422,10 @@
       <c r="C116" t="n">
         <v>999</v>
       </c>
-      <c r="D116" t="n">
-        <v>95030020</v>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E116" t="n">
         <v>0.05</v>
@@ -4021,12 +4435,13 @@
           <t>SMRT1260</t>
         </is>
       </c>
-      <c r="G116" t="n">
-        <v>8908011797754</v>
-      </c>
-      <c r="H116" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>8908011797754</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4040,8 +4455,10 @@
       <c r="C117" t="n">
         <v>60</v>
       </c>
-      <c r="D117" t="n">
-        <v>95030020</v>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E117" t="n">
         <v>0.05</v>
@@ -4051,12 +4468,13 @@
           <t>SMRT1262</t>
         </is>
       </c>
-      <c r="G117" t="n">
-        <v>8906187980031</v>
-      </c>
-      <c r="H117" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>8906187980031</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4070,8 +4488,10 @@
       <c r="C118" t="n">
         <v>669</v>
       </c>
-      <c r="D118" t="n">
-        <v>95030020</v>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E118" t="n">
         <v>0.05</v>
@@ -4081,12 +4501,13 @@
           <t>SMRT1268</t>
         </is>
       </c>
-      <c r="G118" t="n">
-        <v>8908011797815</v>
-      </c>
-      <c r="H118" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>8908011797815</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4100,8 +4521,10 @@
       <c r="C119" t="n">
         <v>869</v>
       </c>
-      <c r="D119" t="n">
-        <v>95030020</v>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E119" t="n">
         <v>0.05</v>
@@ -4111,14 +4534,16 @@
           <t>SMRT1269</t>
         </is>
       </c>
-      <c r="G119" t="n">
-        <v>8908011797822</v>
-      </c>
-      <c r="H119" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I119" t="n">
-        <v>891201</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>8908011797822</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>891201</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -4133,8 +4558,10 @@
       <c r="C120" t="n">
         <v>769</v>
       </c>
-      <c r="D120" t="n">
-        <v>95030020</v>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E120" t="n">
         <v>0.05</v>
@@ -4144,14 +4571,17 @@
           <t>SMRT1270</t>
         </is>
       </c>
-      <c r="G120" t="n">
-        <v>8908011797846</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>8908011797846</t>
+        </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>19825873</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4159,26 +4589,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SMRT1271-MECHBEAS</t>
+          <t>SMRT1271 - Mech Beas</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>669</v>
       </c>
-      <c r="D121" t="n">
-        <v>95030020</v>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E121" t="n">
         <v>0.05</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SMRT1271-MECHBEAS</t>
-        </is>
-      </c>
-      <c r="G121" t="n">
-        <v>8908011797761</v>
-      </c>
+          <t>SMRT1271 - Mech Beas</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>8908011797761</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -4192,8 +4628,10 @@
       <c r="C122" t="n">
         <v>299</v>
       </c>
-      <c r="D122" t="n">
-        <v>95030020</v>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E122" t="n">
         <v>0.05</v>
@@ -4203,12 +4641,13 @@
           <t>SMRT1272</t>
         </is>
       </c>
-      <c r="G122" t="n">
-        <v>8908011797730</v>
-      </c>
-      <c r="H122" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>8908011797730</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -4222,8 +4661,10 @@
       <c r="C123" t="n">
         <v>799</v>
       </c>
-      <c r="D123" t="n">
-        <v>95030020</v>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E123" t="n">
         <v>0.05</v>
@@ -4233,14 +4674,16 @@
           <t>SMRT1273</t>
         </is>
       </c>
-      <c r="G123" t="n">
-        <v>8908011797938</v>
-      </c>
-      <c r="H123" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I123" t="n">
-        <v>645243</v>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>8908011797938</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>645243</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -4255,8 +4698,10 @@
       <c r="C124" t="n">
         <v>869</v>
       </c>
-      <c r="D124" t="n">
-        <v>95030020</v>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E124" t="n">
         <v>0.05</v>
@@ -4266,12 +4711,13 @@
           <t>SMRT1274</t>
         </is>
       </c>
-      <c r="G124" t="n">
-        <v>8908011797839</v>
-      </c>
-      <c r="H124" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>8908011797839</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4285,8 +4731,10 @@
       <c r="C125" t="n">
         <v>669</v>
       </c>
-      <c r="D125" t="n">
-        <v>95030020</v>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E125" t="n">
         <v>0.05</v>
@@ -4296,12 +4744,13 @@
           <t>SMRT1275</t>
         </is>
       </c>
-      <c r="G125" t="n">
-        <v>8908011797778</v>
-      </c>
-      <c r="H125" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>8908011797778</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4315,8 +4764,10 @@
       <c r="C126" t="n">
         <v>649</v>
       </c>
-      <c r="D126" t="n">
-        <v>95030020</v>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E126" t="n">
         <v>0.05</v>
@@ -4326,16 +4777,20 @@
           <t>SMRT1276</t>
         </is>
       </c>
-      <c r="G126" t="n">
-        <v>8908011797808</v>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>8908011797808</t>
+        </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>17856015</t>
         </is>
       </c>
-      <c r="I126" t="n">
-        <v>950782</v>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>950782</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -4350,8 +4805,10 @@
       <c r="C127" t="n">
         <v>769</v>
       </c>
-      <c r="D127" t="n">
-        <v>95030020</v>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E127" t="n">
         <v>0.05</v>
@@ -4361,14 +4818,17 @@
           <t>SMRT1277</t>
         </is>
       </c>
-      <c r="G127" t="n">
-        <v>8908011797853</v>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>8908011797853</t>
+        </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>18481804</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -4382,8 +4842,10 @@
       <c r="C128" t="n">
         <v>849</v>
       </c>
-      <c r="D128" t="n">
-        <v>95030020</v>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E128" t="n">
         <v>0.05</v>
@@ -4393,16 +4855,20 @@
           <t>SMRT1279</t>
         </is>
       </c>
-      <c r="G128" t="n">
-        <v>8908011797877</v>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>8908011797877</t>
+        </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>19050876</t>
         </is>
       </c>
-      <c r="I128" t="n">
-        <v>208840</v>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>208840</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -4417,8 +4883,10 @@
       <c r="C129" t="n">
         <v>1099</v>
       </c>
-      <c r="D129" t="n">
-        <v>95030020</v>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E129" t="n">
         <v>0.05</v>
@@ -4428,12 +4896,13 @@
           <t>SMRT1280</t>
         </is>
       </c>
-      <c r="G129" t="n">
-        <v>8908011797907</v>
-      </c>
-      <c r="H129" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>8908011797907</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -4447,8 +4916,10 @@
       <c r="C130" t="n">
         <v>749</v>
       </c>
-      <c r="D130" t="n">
-        <v>95030020</v>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E130" t="n">
         <v>0.05</v>
@@ -4458,14 +4929,17 @@
           <t>SMRT1281</t>
         </is>
       </c>
-      <c r="G130" t="n">
-        <v>8908011797891</v>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>8908011797891</t>
+        </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>18481805</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -4479,8 +4953,10 @@
       <c r="C131" t="n">
         <v>579</v>
       </c>
-      <c r="D131" t="n">
-        <v>95030020</v>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E131" t="n">
         <v>0.05</v>
@@ -4490,16 +4966,20 @@
           <t>SMRT1282</t>
         </is>
       </c>
-      <c r="G131" t="n">
-        <v>8908011797884</v>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>8908011797884</t>
+        </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>19825874</t>
         </is>
       </c>
-      <c r="I131" t="n">
-        <v>235066</v>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>235066</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -4514,8 +4994,10 @@
       <c r="C132" t="n">
         <v>919</v>
       </c>
-      <c r="D132" t="n">
-        <v>95030020</v>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E132" t="n">
         <v>0.05</v>
@@ -4525,12 +5007,13 @@
           <t>SMRT1283SM</t>
         </is>
       </c>
-      <c r="G132" t="n">
-        <v>8906187980079</v>
-      </c>
-      <c r="H132" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>8906187980079</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -4544,8 +5027,10 @@
       <c r="C133" t="n">
         <v>289</v>
       </c>
-      <c r="D133" t="n">
-        <v>95030020</v>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E133" t="n">
         <v>0.05</v>
@@ -4555,12 +5040,13 @@
           <t>SMRT1292</t>
         </is>
       </c>
-      <c r="G133" t="n">
-        <v>8908011797914</v>
-      </c>
-      <c r="H133" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>8908011797914</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -4574,8 +5060,10 @@
       <c r="C134" t="n">
         <v>769</v>
       </c>
-      <c r="D134" t="n">
-        <v>95030020</v>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E134" t="n">
         <v>0.05</v>
@@ -4585,14 +5073,17 @@
           <t>SMRT1293</t>
         </is>
       </c>
-      <c r="G134" t="n">
-        <v>8908011797952</v>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>8908011797952</t>
+        </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>19050877</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -4606,8 +5097,10 @@
       <c r="C135" t="n">
         <v>749</v>
       </c>
-      <c r="D135" t="n">
-        <v>95030020</v>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E135" t="n">
         <v>0.05</v>
@@ -4617,16 +5110,20 @@
           <t>SMRT1295</t>
         </is>
       </c>
-      <c r="G135" t="n">
-        <v>8906187980000</v>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>8906187980000</t>
+        </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>19287676</t>
         </is>
       </c>
-      <c r="I135" t="n">
-        <v>560273</v>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>560273</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -4641,8 +5138,10 @@
       <c r="C136" t="n">
         <v>1299</v>
       </c>
-      <c r="D136" t="n">
-        <v>95030010</v>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>95030010</t>
+        </is>
       </c>
       <c r="E136" t="n">
         <v>0.18</v>
@@ -4652,14 +5151,17 @@
           <t>SMRT1296</t>
         </is>
       </c>
-      <c r="G136" t="n">
-        <v>8906187980109</v>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>8906187980109</t>
+        </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>21239906</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -4673,8 +5175,10 @@
       <c r="C137" t="n">
         <v>769</v>
       </c>
-      <c r="D137" t="n">
-        <v>95030020</v>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E137" t="n">
         <v>0.05</v>
@@ -4684,12 +5188,13 @@
           <t>SMRT1297</t>
         </is>
       </c>
-      <c r="G137" t="n">
-        <v>8908011797983</v>
-      </c>
-      <c r="H137" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>8908011797983</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -4703,8 +5208,10 @@
       <c r="C138" t="n">
         <v>799</v>
       </c>
-      <c r="D138" t="n">
-        <v>95030020</v>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E138" t="n">
         <v>0.05</v>
@@ -4714,14 +5221,17 @@
           <t>SMRT1298</t>
         </is>
       </c>
-      <c r="G138" t="n">
-        <v>8908011797990</v>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>8908011797990</t>
+        </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>19825877</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -4735,8 +5245,10 @@
       <c r="C139" t="n">
         <v>599</v>
       </c>
-      <c r="D139" t="n">
-        <v>95030020</v>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E139" t="n">
         <v>0.05</v>
@@ -4746,16 +5258,20 @@
           <t>SMRT1299</t>
         </is>
       </c>
-      <c r="G139" t="n">
-        <v>8908011797969</v>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>8908011797969</t>
+        </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>19825875</t>
         </is>
       </c>
-      <c r="I139" t="n">
-        <v>864545</v>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>864545</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -4770,8 +5286,10 @@
       <c r="C140" t="n">
         <v>699</v>
       </c>
-      <c r="D140" t="n">
-        <v>95030020</v>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E140" t="n">
         <v>0.05</v>
@@ -4781,12 +5299,13 @@
           <t>SMRT1300</t>
         </is>
       </c>
-      <c r="G140" t="n">
-        <v>8906187980017</v>
-      </c>
-      <c r="H140" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>8906187980017</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -4800,8 +5319,10 @@
       <c r="C141" t="n">
         <v>1099</v>
       </c>
-      <c r="D141" t="n">
-        <v>95030020</v>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E141" t="n">
         <v>0.05</v>
@@ -4811,14 +5332,17 @@
           <t>SMRT1301</t>
         </is>
       </c>
-      <c r="G141" t="n">
-        <v>8906187980147</v>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>8906187980147</t>
+        </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>20586288</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -4832,8 +5356,10 @@
       <c r="C142" t="n">
         <v>999</v>
       </c>
-      <c r="D142" t="n">
-        <v>95030010</v>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>95030010</t>
+        </is>
       </c>
       <c r="E142" t="n">
         <v>0.18</v>
@@ -4843,14 +5369,17 @@
           <t>SMRT1302</t>
         </is>
       </c>
-      <c r="G142" t="n">
-        <v>8906187980178</v>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>8906187980178</t>
+        </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>20586289</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -4864,8 +5393,10 @@
       <c r="C143" t="n">
         <v>1149</v>
       </c>
-      <c r="D143" t="n">
-        <v>95030020</v>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E143" t="n">
         <v>0.05</v>
@@ -4875,16 +5406,20 @@
           <t>SMRT1303</t>
         </is>
       </c>
-      <c r="G143" t="n">
-        <v>8906187980345</v>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>8906187980345</t>
+        </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>22032971</t>
         </is>
       </c>
-      <c r="I143" t="n">
-        <v>822097</v>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>822097</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -4899,8 +5434,10 @@
       <c r="C144" t="n">
         <v>869</v>
       </c>
-      <c r="D144" t="n">
-        <v>95030020</v>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E144" t="n">
         <v>0.05</v>
@@ -4910,14 +5447,17 @@
           <t>SMRT1305</t>
         </is>
       </c>
-      <c r="G144" t="n">
-        <v>8906187980116</v>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>8906187980116</t>
+        </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>21239905</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -4931,8 +5471,10 @@
       <c r="C145" t="n">
         <v>799</v>
       </c>
-      <c r="D145" t="n">
-        <v>95030020</v>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E145" t="n">
         <v>0.05</v>
@@ -4942,14 +5484,17 @@
           <t>SMRT1309</t>
         </is>
       </c>
-      <c r="G145" t="n">
-        <v>8906187980222</v>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>8906187980222</t>
+        </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
           <t>21239909</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4963,8 +5508,10 @@
       <c r="C146" t="n">
         <v>749</v>
       </c>
-      <c r="D146" t="n">
-        <v>95030020</v>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E146" t="n">
         <v>0.05</v>
@@ -4974,14 +5521,17 @@
           <t>SMRT1310</t>
         </is>
       </c>
-      <c r="G146" t="n">
-        <v>8906187980314</v>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>8906187980314</t>
+        </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
           <t>22032972</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -4995,8 +5545,10 @@
       <c r="C147" t="n">
         <v>669</v>
       </c>
-      <c r="D147" t="n">
-        <v>95030020</v>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E147" t="n">
         <v>0.05</v>
@@ -5006,14 +5558,17 @@
           <t>SMRT1312</t>
         </is>
       </c>
-      <c r="G147" t="n">
-        <v>8906187980208</v>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>8906187980208</t>
+        </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>21239907</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -5027,8 +5582,10 @@
       <c r="C148" t="n">
         <v>549</v>
       </c>
-      <c r="D148" t="n">
-        <v>95030020</v>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E148" t="n">
         <v>0.05</v>
@@ -5038,12 +5595,13 @@
           <t>SMRT1313</t>
         </is>
       </c>
-      <c r="G148" t="n">
-        <v>8906187980239</v>
-      </c>
-      <c r="H148" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>8906187980239</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -5057,8 +5615,10 @@
       <c r="C149" t="n">
         <v>669</v>
       </c>
-      <c r="D149" t="n">
-        <v>95030020</v>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E149" t="n">
         <v>0.05</v>
@@ -5068,14 +5628,17 @@
           <t>SMRT1315</t>
         </is>
       </c>
-      <c r="G149" t="n">
-        <v>8906187980215</v>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>8906187980215</t>
+        </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
           <t>21239908</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -5089,8 +5652,10 @@
       <c r="C150" t="n">
         <v>599</v>
       </c>
-      <c r="D150" t="n">
-        <v>95030020</v>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E150" t="n">
         <v>0.05</v>
@@ -5100,14 +5665,17 @@
           <t>SMRT1320</t>
         </is>
       </c>
-      <c r="G150" t="n">
-        <v>8906187980246</v>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>8906187980246</t>
+        </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
           <t>21239910</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -5121,8 +5689,10 @@
       <c r="C151" t="n">
         <v>749</v>
       </c>
-      <c r="D151" t="n">
-        <v>95030020</v>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E151" t="n">
         <v>0.05</v>
@@ -5132,14 +5702,17 @@
           <t>SMRT1321</t>
         </is>
       </c>
-      <c r="G151" t="n">
-        <v>8906187980260</v>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>8906187980260</t>
+        </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
           <t>21239911</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -5153,8 +5726,10 @@
       <c r="C152" t="n">
         <v>799</v>
       </c>
-      <c r="D152" t="n">
-        <v>95030020</v>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E152" t="n">
         <v>0.05</v>
@@ -5164,14 +5739,17 @@
           <t>SMRT1322</t>
         </is>
       </c>
-      <c r="G152" t="n">
-        <v>8906187980277</v>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>8906187980277</t>
+        </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
           <t>21239912</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5185,8 +5763,10 @@
       <c r="C153" t="n">
         <v>1499</v>
       </c>
-      <c r="D153" t="n">
-        <v>95030020</v>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E153" t="n">
         <v>0.05</v>
@@ -5196,12 +5776,13 @@
           <t>SMRT1323</t>
         </is>
       </c>
-      <c r="G153" t="n">
-        <v>8906187980482</v>
-      </c>
-      <c r="H153" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>8906187980482</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -5215,8 +5796,10 @@
       <c r="C154" t="n">
         <v>749</v>
       </c>
-      <c r="D154" t="n">
-        <v>95030020</v>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E154" t="n">
         <v>0.05</v>
@@ -5226,14 +5809,17 @@
           <t>SMRT1324</t>
         </is>
       </c>
-      <c r="G154" t="n">
-        <v>8906187980321</v>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>8906187980321</t>
+        </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
           <t>22032969</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -5247,8 +5833,10 @@
       <c r="C155" t="n">
         <v>899</v>
       </c>
-      <c r="D155" t="n">
-        <v>95030020</v>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E155" t="n">
         <v>0.05</v>
@@ -5258,14 +5846,17 @@
           <t>SMRT1325</t>
         </is>
       </c>
-      <c r="G155" t="n">
-        <v>8906187980369</v>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>8906187980369</t>
+        </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
           <t>22032973</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5279,8 +5870,10 @@
       <c r="C156" t="n">
         <v>529</v>
       </c>
-      <c r="D156" t="n">
-        <v>95030020</v>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E156" t="n">
         <v>0.05</v>
@@ -5290,12 +5883,13 @@
           <t>SMRT1326</t>
         </is>
       </c>
-      <c r="G156" t="n">
-        <v>8906187980253</v>
-      </c>
-      <c r="H156" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>8906187980253</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -5309,8 +5903,10 @@
       <c r="C157" t="n">
         <v>699</v>
       </c>
-      <c r="D157" t="n">
-        <v>95030020</v>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E157" t="n">
         <v>0.05</v>
@@ -5320,12 +5916,13 @@
           <t>SMRT1328</t>
         </is>
       </c>
-      <c r="G157" t="n">
-        <v>8906187980284</v>
-      </c>
-      <c r="H157" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>8906187980284</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -5339,8 +5936,10 @@
       <c r="C158" t="n">
         <v>559</v>
       </c>
-      <c r="D158" t="n">
-        <v>95030020</v>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E158" t="n">
         <v>0.05</v>
@@ -5350,12 +5949,13 @@
           <t>SMRT1329</t>
         </is>
       </c>
-      <c r="G158" t="n">
-        <v>8906187980291</v>
-      </c>
-      <c r="H158" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>8906187980291</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -5369,8 +5969,10 @@
       <c r="C159" t="n">
         <v>699</v>
       </c>
-      <c r="D159" t="n">
-        <v>95030020</v>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E159" t="n">
         <v>0.05</v>
@@ -5380,14 +5982,17 @@
           <t>SMRT1333</t>
         </is>
       </c>
-      <c r="G159" t="n">
-        <v>8906187980338</v>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>8906187980338</t>
+        </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
           <t>22032970</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -5401,8 +6006,10 @@
       <c r="C160" t="n">
         <v>1149</v>
       </c>
-      <c r="D160" t="n">
-        <v>95030020</v>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E160" t="n">
         <v>0.05</v>
@@ -5412,14 +6019,17 @@
           <t>SMRT1334</t>
         </is>
       </c>
-      <c r="G160" t="n">
-        <v>8906187980376</v>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>8906187980376</t>
+        </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
           <t>22032974</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -5433,8 +6043,10 @@
       <c r="C161" t="n">
         <v>649</v>
       </c>
-      <c r="D161" t="n">
-        <v>95030020</v>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E161" t="n">
         <v>0.05</v>
@@ -5444,12 +6056,13 @@
           <t>SMRT1335</t>
         </is>
       </c>
-      <c r="G161" t="n">
-        <v>8906187980383</v>
-      </c>
-      <c r="H161" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>8906187980383</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -5463,8 +6076,10 @@
       <c r="C162" t="n">
         <v>699</v>
       </c>
-      <c r="D162" t="n">
-        <v>95030020</v>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E162" t="n">
         <v>0.05</v>
@@ -5474,14 +6089,17 @@
           <t>SMRT1336</t>
         </is>
       </c>
-      <c r="G162" t="n">
-        <v>8906187980307</v>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>8906187980307</t>
+        </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
           <t>21239913</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -5495,8 +6113,10 @@
       <c r="C163" t="n">
         <v>749</v>
       </c>
-      <c r="D163" t="n">
-        <v>95030020</v>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E163" t="n">
         <v>0.05</v>
@@ -5506,14 +6126,17 @@
           <t>SMRT1337</t>
         </is>
       </c>
-      <c r="G163" t="n">
-        <v>8906187980352</v>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>8906187980352</t>
+        </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
           <t>22032975</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -5527,8 +6150,10 @@
       <c r="C164" t="n">
         <v>699</v>
       </c>
-      <c r="D164" t="n">
-        <v>95030020</v>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E164" t="n">
         <v>0.05</v>
@@ -5538,14 +6163,17 @@
           <t>SMRT1339</t>
         </is>
       </c>
-      <c r="G164" t="n">
-        <v>8906187980413</v>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>8906187980413</t>
+        </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
           <t>22032978</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -5559,8 +6187,10 @@
       <c r="C165" t="n">
         <v>599</v>
       </c>
-      <c r="D165" t="n">
-        <v>95030020</v>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E165" t="n">
         <v>0.05</v>
@@ -5570,14 +6200,17 @@
           <t>SMRT1340</t>
         </is>
       </c>
-      <c r="G165" t="n">
-        <v>8906187980390</v>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>8906187980390</t>
+        </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
           <t>22032977</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -5591,8 +6224,10 @@
       <c r="C166" t="n">
         <v>899</v>
       </c>
-      <c r="D166" t="n">
-        <v>95030020</v>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E166" t="n">
         <v>0.05</v>
@@ -5602,12 +6237,13 @@
           <t>SMRT1344</t>
         </is>
       </c>
-      <c r="G166" t="n">
-        <v>8906187980475</v>
-      </c>
-      <c r="H166" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>8906187980475</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -5621,8 +6257,10 @@
       <c r="C167" t="n">
         <v>1099</v>
       </c>
-      <c r="D167" t="n">
-        <v>95030020</v>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E167" t="n">
         <v>0.05</v>
@@ -5632,12 +6270,13 @@
           <t>SMRT1345</t>
         </is>
       </c>
-      <c r="G167" t="n">
-        <v>8906187980468</v>
-      </c>
-      <c r="H167" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>8906187980468</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -5651,8 +6290,10 @@
       <c r="C168" t="n">
         <v>699</v>
       </c>
-      <c r="D168" t="n">
-        <v>95030020</v>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E168" t="n">
         <v>0.05</v>
@@ -5662,14 +6303,17 @@
           <t>SMRT1346</t>
         </is>
       </c>
-      <c r="G168" t="n">
-        <v>8906187980420</v>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>8906187980420</t>
+        </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
           <t>22032979</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -5683,8 +6327,10 @@
       <c r="C169" t="n">
         <v>799</v>
       </c>
-      <c r="D169" t="n">
-        <v>95030020</v>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E169" t="n">
         <v>0.05</v>
@@ -5694,12 +6340,13 @@
           <t>SMRT1347</t>
         </is>
       </c>
-      <c r="G169" t="n">
-        <v>8906187980444</v>
-      </c>
-      <c r="H169" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>8906187980444</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -5713,8 +6360,10 @@
       <c r="C170" t="n">
         <v>799</v>
       </c>
-      <c r="D170" t="n">
-        <v>95030020</v>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E170" t="n">
         <v>0.05</v>
@@ -5724,12 +6373,13 @@
           <t>SMRT1348</t>
         </is>
       </c>
-      <c r="G170" t="n">
-        <v>8906187980451</v>
-      </c>
-      <c r="H170" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>8906187980451</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -5743,8 +6393,10 @@
       <c r="C171" t="n">
         <v>849</v>
       </c>
-      <c r="D171" t="n">
-        <v>95030020</v>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
       </c>
       <c r="E171" t="n">
         <v>0.05</v>
@@ -5754,12 +6406,145 @@
           <t>SMRT1364</t>
         </is>
       </c>
-      <c r="G171" t="n">
-        <v>8906187980512</v>
-      </c>
-      <c r="H171" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>8906187980512</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>172</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SMRT1350</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>SMRT1350</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>8906187980536</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>173</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SMRT1358</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>349</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>SMRT1358</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>8906187980628</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>174</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SMRT1360</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>299</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>SMRT1360</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>8906187980635</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>175</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SMRT1369</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>799</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>SMRT1369</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>8906187980666</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5845,9 +6630,15 @@
       <c r="C3" t="n">
         <v>0.47619</v>
       </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="n">
         <v>0.533898</v>
       </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5863,9 +6654,15 @@
       <c r="C4" t="n">
         <v>0.47619</v>
       </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
       <c r="E4" t="n">
         <v>0.533898</v>
       </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5881,9 +6678,15 @@
       <c r="C5" t="n">
         <v>0.47619</v>
       </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="n">
         <v>0.533898</v>
       </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5899,9 +6702,15 @@
       <c r="C6" t="n">
         <v>0.47619</v>
       </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
       <c r="E6" t="n">
         <v>0.533898</v>
       </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5917,9 +6726,15 @@
       <c r="C7" t="n">
         <v>0.47619</v>
       </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
       <c r="E7" t="n">
         <v>0.533898</v>
       </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5935,215 +6750,856 @@
       <c r="C8" t="n">
         <v>0.47619</v>
       </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" t="n">
         <v>0.533898</v>
       </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BABA SALES</t>
+          <t>ARCADE TRADING</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BABA SALES</t>
+          <t>ARCADE TRADING</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0.4762</v>
       </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
       <c r="E9" t="n">
         <v>0.5339</v>
       </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LOOKS AND MUCH MORE</t>
+          <t>ZENTRIX INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LOOKS AND MUCH MORE</t>
+          <t>ZENTRIX INDIA PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HAI BABY</t>
+          <t>PUSHP CREATIONS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HAI BABY</t>
+          <t>PUSHP CREATIONS</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0.4762</v>
       </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
       <c r="E11" t="n">
         <v>0.5339</v>
       </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TEJAL INTERNATIONAL</t>
+          <t>MECTRONIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TEJAL INTERNATIONAL</t>
+          <t>MECTRONIC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.4762</v>
+        <v>0.5047</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5339</v>
+        <v>0.5593</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SPILLBOX INNOVATION PRIVATE</t>
+          <t>PAL TRADELINK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SPILLBOX INNOVATION PRIVATE</t>
+          <t>PAL TRADELINK</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5238</v>
+        <v>0.4762</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5763</v>
+        <v>0.5339</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KITSONS KONDAPUR</t>
+          <t>ADVIRAA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KITSONS KONDAPUR</t>
+          <t>ADVIRAA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4915</v>
+        <v>0.5339</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SAI TAK AND CO (Boston Books,Stationery &amp; Toys)</t>
+          <t>RK Enterprises</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAI TAK AND CO (Boston Books,Stationery &amp; Toys)</t>
+          <t>RK Enterprises</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4286</v>
+        <v>0.5238</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4915</v>
+        <v>0.5763</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KITSONS GACHIBOWLI</t>
+          <t>Pune Rural Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KITSONS GACHIBOWLI</t>
+          <t>Pune Rural Marketing</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4915</v>
+        <v>0.5339</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KITSONS GOLDEN MILE</t>
+          <t>POOJA SALES CORP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KITSONS GOLDEN MILE</t>
+          <t>POOJA SALES CORP</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4915</v>
+        <v>0.5339</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KITSONS KOKAPET</t>
+          <t>OZI TECHNOLOGIES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KITSONS KOKAPET</t>
+          <t>OZI TECHNOLOGIES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4915</v>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
+        <v>0.5339</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GOOD LUCK AGENCIES</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GOOD LUCK AGENCIES</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>G MARKETING</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>G MARKETING</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R &amp; S ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>R &amp; S ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ELARA AND COMPANY</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ELARA AND COMPANY</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SPILLBOX INNOVATION PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SPILLBOX INNOVATION PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MAA ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MAA ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BANSAL BOOK AND STATIONERS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BANSAL BOOK AND STATIONERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TOYS TOWN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TOYS TOWN</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SHREE BALAJI ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SHREE BALAJI ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BABA SALES</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BABA SALES</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EQUATOR TRADE HOUSE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EQUATOR TRADE HOUSE</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>THEME AMBIENCE ENTERPRISES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>THEME AMBIENCE ENTERPRISES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TEJAL INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TEJAL INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MILLENNIUM INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MILLENNIUM INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SK ENTERPRISE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SK ENTERPRISE</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.5744</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SHUBHAM ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SHUBHAM ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ANAND GIFT EMPORIUM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ANAND GIFT EMPORIUM</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>RAJESH TRADERS</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>RAJESH TRADERS</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>VIJAY SALES</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>VIJAY SALES</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ZIPPYCUBS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ZIPPYCUBS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SEEMA AND SONS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SEEMA AND SONS</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AGGARWAL MARKETING CO.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AGGARWAL MARKETING CO.</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>H S ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H S ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MODERN AGENCIES</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MODERN AGENCIES</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="44"/>
     <row r="45"/>
     <row r="46"/>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -494,8 +494,6 @@
           <t>8908006537105</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -532,7 +530,6 @@
           <t>8606916</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -564,8 +561,6 @@
           <t>8908006537129</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -597,8 +592,6 @@
           <t>8908006537136</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -630,8 +623,6 @@
           <t>8908006537167</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -663,8 +654,6 @@
           <t>8908006537174</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -696,8 +685,6 @@
           <t>8908006537204</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -729,8 +716,6 @@
           <t>8908006537211</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -762,8 +747,6 @@
           <t>8908006537228</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -795,8 +778,6 @@
           <t>8908006537235</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -828,8 +809,6 @@
           <t>8908006537242</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -861,8 +840,6 @@
           <t>8908006537259</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -894,8 +871,6 @@
           <t>8908006537266</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -927,8 +902,6 @@
           <t>8908006537273</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -960,8 +933,6 @@
           <t>8908006537303</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -998,7 +969,6 @@
           <t>8606924</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1030,8 +1000,6 @@
           <t>8908006537327</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1063,8 +1031,6 @@
           <t>8908006537334</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1096,8 +1062,6 @@
           <t>8908006537341</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1129,8 +1093,6 @@
           <t>8908006537365</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1162,7 +1124,6 @@
           <t>8908006537396</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>61820</t>
@@ -1199,8 +1160,6 @@
           <t>8908006537419</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1232,8 +1191,6 @@
           <t>8908006537426</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1265,8 +1222,6 @@
           <t>8908006537433</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1298,8 +1253,6 @@
           <t>8908006537440</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1331,8 +1284,6 @@
           <t>8908006537457</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1364,8 +1315,6 @@
           <t>8908006537464</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1397,7 +1346,6 @@
           <t>8908006537471</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>64139</t>
@@ -1434,8 +1382,6 @@
           <t>8908006537488</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1467,8 +1413,6 @@
           <t>8908006537501</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1500,8 +1444,6 @@
           <t>8908006537556</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1533,8 +1475,6 @@
           <t>8908006537570</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1566,8 +1506,6 @@
           <t>8908006537631</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1599,8 +1537,6 @@
           <t>8908006537716</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1632,8 +1568,6 @@
           <t>8908006537723</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1665,8 +1599,6 @@
           <t>8908006537730</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1698,8 +1630,6 @@
           <t>8908006537778</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1731,8 +1661,6 @@
           <t>8908006537785</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1764,8 +1692,6 @@
           <t>8908006537792</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1797,8 +1723,6 @@
           <t>8908006537808</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1830,8 +1754,6 @@
           <t>8908006537815</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1863,8 +1785,6 @@
           <t>8908006537822</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1896,8 +1816,6 @@
           <t>8908006537853</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1929,8 +1847,6 @@
           <t>8908006537860</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1962,8 +1878,6 @@
           <t>8908006537877</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1995,8 +1909,6 @@
           <t>8908006537884</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2033,7 +1945,6 @@
           <t>8606931</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2065,8 +1976,6 @@
           <t>8908006537914</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2098,8 +2007,6 @@
           <t>8908006537921</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2131,8 +2038,6 @@
           <t>8908006537983</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2164,8 +2069,6 @@
           <t>8908006537990</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2238,8 +2141,6 @@
           <t>8908006537389</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2271,8 +2172,6 @@
           <t>8908006537549</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2304,8 +2203,6 @@
           <t>8908006537372</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2337,8 +2234,6 @@
           <t>8908006537969</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2370,8 +2265,6 @@
           <t>8908006537976</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2403,8 +2296,6 @@
           <t>8908011797020</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2436,8 +2327,6 @@
           <t>8908011797037</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2469,8 +2358,6 @@
           <t>8908011797051</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2502,8 +2389,6 @@
           <t>8908011797075</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2535,8 +2420,6 @@
           <t>8908011797068</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2568,8 +2451,6 @@
           <t>8908011797136</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2601,8 +2482,6 @@
           <t>8908011797082</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2762,7 +2641,6 @@
           <t>8947250</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2794,8 +2672,6 @@
           <t>8908011797129</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2909,8 +2785,6 @@
           <t>8908011797167</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2942,8 +2816,6 @@
           <t>8908011797174</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2975,8 +2847,6 @@
           <t>8908011797181</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3008,8 +2878,6 @@
           <t>8908011797198</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3082,8 +2950,6 @@
           <t>8908011797242</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3115,8 +2981,6 @@
           <t>8908011797273</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3189,8 +3053,6 @@
           <t>8908011797280</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3263,8 +3125,6 @@
           <t>8908011797235</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3296,8 +3156,6 @@
           <t>8908011797266</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3329,8 +3187,6 @@
           <t>8908011797310</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3362,8 +3218,6 @@
           <t>8908011797334</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3395,8 +3249,6 @@
           <t>8908011797426</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3510,8 +3362,6 @@
           <t>8908006537587</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3543,8 +3393,6 @@
           <t>8908006537594</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3576,8 +3424,6 @@
           <t>8908006537709</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3609,8 +3455,6 @@
           <t>8908011797471</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3683,7 +3527,6 @@
           <t>8908011797464</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>481367</t>
@@ -3761,8 +3604,6 @@
           <t>8908011797570</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3794,8 +3635,6 @@
           <t>8908011797792</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3868,8 +3707,6 @@
           <t>8908011797532</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3901,8 +3738,6 @@
           <t>8908011797563</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3934,8 +3769,6 @@
           <t>8908011797556</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3967,8 +3800,6 @@
           <t>8908011797587</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4041,8 +3872,6 @@
           <t>8908011797617</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4074,7 +3903,6 @@
           <t>8908011797648</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>458614</t>
@@ -4116,7 +3944,6 @@
           <t>14626588</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4148,8 +3975,6 @@
           <t>8908011797624</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4186,7 +4011,6 @@
           <t>17856011</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4259,8 +4083,6 @@
           <t>8908011797662</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -4333,8 +4155,6 @@
           <t>8908011797723</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -4407,8 +4227,6 @@
           <t>8908011797709</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4440,8 +4258,6 @@
           <t>8908011797754</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4473,8 +4289,6 @@
           <t>8906187980031</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4506,8 +4320,6 @@
           <t>8908011797815</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4539,7 +4351,6 @@
           <t>8908011797822</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>891201</t>
@@ -4581,7 +4392,6 @@
           <t>19825873</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4613,8 +4423,6 @@
           <t>8908011797761</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -4646,8 +4454,6 @@
           <t>8908011797730</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -4679,7 +4485,6 @@
           <t>8908011797938</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>645243</t>
@@ -4716,8 +4521,6 @@
           <t>8908011797839</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4749,8 +4552,6 @@
           <t>8908011797778</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4828,7 +4629,6 @@
           <t>18481804</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -4901,8 +4701,6 @@
           <t>8908011797907</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -4939,7 +4737,6 @@
           <t>18481805</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -5012,8 +4809,6 @@
           <t>8906187980079</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5045,8 +4840,6 @@
           <t>8908011797914</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -5083,7 +4876,6 @@
           <t>19050877</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5161,7 +4953,6 @@
           <t>21239906</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -5193,8 +4984,6 @@
           <t>8908011797983</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -5231,7 +5020,6 @@
           <t>19825877</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -5304,8 +5092,6 @@
           <t>8906187980017</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -5342,7 +5128,6 @@
           <t>20586288</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -5379,7 +5164,6 @@
           <t>20586289</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -5457,7 +5241,6 @@
           <t>21239905</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -5494,7 +5277,6 @@
           <t>21239909</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -5531,7 +5313,6 @@
           <t>22032972</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -5568,7 +5349,6 @@
           <t>21239907</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -5600,8 +5380,6 @@
           <t>8906187980239</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -5638,7 +5416,6 @@
           <t>21239908</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -5675,7 +5452,6 @@
           <t>21239910</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -5712,7 +5488,6 @@
           <t>21239911</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -5749,7 +5524,6 @@
           <t>21239912</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5781,8 +5555,6 @@
           <t>8906187980482</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -5819,7 +5591,6 @@
           <t>22032969</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -5856,7 +5627,6 @@
           <t>22032973</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5888,8 +5658,6 @@
           <t>8906187980253</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -5921,8 +5689,6 @@
           <t>8906187980284</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -5954,8 +5720,6 @@
           <t>8906187980291</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -5992,7 +5756,6 @@
           <t>22032970</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -6029,7 +5792,6 @@
           <t>22032974</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -6061,8 +5823,6 @@
           <t>8906187980383</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -6099,7 +5859,6 @@
           <t>21239913</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -6136,7 +5895,6 @@
           <t>22032975</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -6173,7 +5931,6 @@
           <t>22032978</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -6210,7 +5967,6 @@
           <t>22032977</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -6242,8 +5998,6 @@
           <t>8906187980475</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -6275,8 +6029,6 @@
           <t>8906187980468</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -6313,7 +6065,6 @@
           <t>22032979</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -6345,8 +6096,6 @@
           <t>8906187980444</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -6378,8 +6127,6 @@
           <t>8906187980451</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -6411,8 +6158,6 @@
           <t>8906187980512</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -6444,8 +6189,6 @@
           <t>8906187980536</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -6477,8 +6220,6 @@
           <t>8906187980628</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -6510,8 +6251,6 @@
           <t>8906187980635</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -6543,8 +6282,6 @@
           <t>8906187980666</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6557,7 +6294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7600,63 +7337,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6280,6 +6280,54 @@
       <c r="G175" t="inlineStr">
         <is>
           <t>8906187980666</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SMRT1368</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>999</v>
+      </c>
+      <c r="D176" t="n">
+        <v>95030020</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>SMRT1368</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SMRT1355</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1299</v>
+      </c>
+      <c r="D177" t="n">
+        <v>95030020</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>SMRT1355</t>
         </is>
       </c>
     </row>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6326,6 +6326,54 @@
         <v>0.05</v>
       </c>
       <c r="F177" t="inlineStr">
+        <is>
+          <t>SMRT1355</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SMRT1368</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>999</v>
+      </c>
+      <c r="D178" t="n">
+        <v>95030020</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>SMRT1368</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SMRT1355</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1299</v>
+      </c>
+      <c r="D179" t="n">
+        <v>95030020</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F179" t="inlineStr">
         <is>
           <t>SMRT1355</t>
         </is>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I179"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6326,54 +6326,6 @@
         <v>0.05</v>
       </c>
       <c r="F177" t="inlineStr">
-        <is>
-          <t>SMRT1355</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>177</v>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>SMRT1368</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>999</v>
-      </c>
-      <c r="D178" t="n">
-        <v>95030020</v>
-      </c>
-      <c r="E178" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>SMRT1368</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>178</v>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>SMRT1355</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>1299</v>
-      </c>
-      <c r="D179" t="n">
-        <v>95030020</v>
-      </c>
-      <c r="E179" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F179" t="inlineStr">
         <is>
           <t>SMRT1355</t>
         </is>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -6285,7 +6285,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -6306,10 +6306,13 @@
           <t>SMRT1368</t>
         </is>
       </c>
+      <c r="G176" t="n">
+        <v>8906187980659</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -6317,7 +6320,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1299</v>
+        <v>699</v>
       </c>
       <c r="D177" t="n">
         <v>95030020</v>
@@ -6329,6 +6332,9 @@
         <is>
           <t>SMRT1355</t>
         </is>
+      </c>
+      <c r="G177" t="n">
+        <v>8906187980505</v>
       </c>
     </row>
   </sheetData>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:I178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6335,6 +6335,33 @@
       </c>
       <c r="G177" t="n">
         <v>8906187980505</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>178</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SMRT1999</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>699</v>
+      </c>
+      <c r="D178" t="n">
+        <v>95030020</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>SMRT1999</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>8906187999999</v>
       </c>
     </row>
   </sheetData>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I178"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6335,33 +6335,6 @@
       </c>
       <c r="G177" t="n">
         <v>8906187980505</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>178</v>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>SMRT1999</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>699</v>
-      </c>
-      <c r="D178" t="n">
-        <v>95030020</v>
-      </c>
-      <c r="E178" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>SMRT1999</t>
-        </is>
-      </c>
-      <c r="G178" t="n">
-        <v>8906187999999</v>
       </c>
     </row>
   </sheetData>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:I178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,8 @@
       <c r="C2" t="n">
         <v>969</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D2" t="n">
+        <v>95030020</v>
       </c>
       <c r="E2" t="n">
         <v>0.05</v>
@@ -489,10 +487,8 @@
           <t>SMRT1011</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>8908006537105</t>
-        </is>
+      <c r="G2" t="n">
+        <v>8908006537105</v>
       </c>
     </row>
     <row r="3">
@@ -507,10 +503,8 @@
       <c r="C3" t="n">
         <v>1059</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D3" t="n">
+        <v>95030020</v>
       </c>
       <c r="E3" t="n">
         <v>0.05</v>
@@ -520,15 +514,11 @@
           <t>SMRT1012</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>8908006537112</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>8606916</t>
-        </is>
+      <c r="G3" t="n">
+        <v>8908006537112</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8606916</v>
       </c>
     </row>
     <row r="4">
@@ -543,10 +533,8 @@
       <c r="C4" t="n">
         <v>969</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D4" t="n">
+        <v>95030020</v>
       </c>
       <c r="E4" t="n">
         <v>0.05</v>
@@ -556,10 +544,8 @@
           <t>SMRT1013</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>8908006537129</t>
-        </is>
+      <c r="G4" t="n">
+        <v>8908006537129</v>
       </c>
     </row>
     <row r="5">
@@ -574,10 +560,8 @@
       <c r="C5" t="n">
         <v>969</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D5" t="n">
+        <v>95030020</v>
       </c>
       <c r="E5" t="n">
         <v>0.05</v>
@@ -587,10 +571,8 @@
           <t>SMRT1014</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>8908006537136</t>
-        </is>
+      <c r="G5" t="n">
+        <v>8908006537136</v>
       </c>
     </row>
     <row r="6">
@@ -605,10 +587,8 @@
       <c r="C6" t="n">
         <v>1159</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D6" t="n">
+        <v>95030020</v>
       </c>
       <c r="E6" t="n">
         <v>0.05</v>
@@ -618,10 +598,8 @@
           <t>SMRT1017</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>8908006537167</t>
-        </is>
+      <c r="G6" t="n">
+        <v>8908006537167</v>
       </c>
     </row>
     <row r="7">
@@ -636,10 +614,8 @@
       <c r="C7" t="n">
         <v>1349</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D7" t="n">
+        <v>95030020</v>
       </c>
       <c r="E7" t="n">
         <v>0.05</v>
@@ -649,10 +625,8 @@
           <t>SMRT1018</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>8908006537174</t>
-        </is>
+      <c r="G7" t="n">
+        <v>8908006537174</v>
       </c>
     </row>
     <row r="8">
@@ -667,10 +641,8 @@
       <c r="C8" t="n">
         <v>339</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D8" t="n">
+        <v>95030020</v>
       </c>
       <c r="E8" t="n">
         <v>0.05</v>
@@ -680,10 +652,8 @@
           <t>SMRT1021</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>8908006537204</t>
-        </is>
+      <c r="G8" t="n">
+        <v>8908006537204</v>
       </c>
     </row>
     <row r="9">
@@ -698,10 +668,8 @@
       <c r="C9" t="n">
         <v>339</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D9" t="n">
+        <v>95030020</v>
       </c>
       <c r="E9" t="n">
         <v>0.05</v>
@@ -711,10 +679,8 @@
           <t>SMRT1022</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>8908006537211</t>
-        </is>
+      <c r="G9" t="n">
+        <v>8908006537211</v>
       </c>
     </row>
     <row r="10">
@@ -729,10 +695,8 @@
       <c r="C10" t="n">
         <v>339</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D10" t="n">
+        <v>95030020</v>
       </c>
       <c r="E10" t="n">
         <v>0.05</v>
@@ -742,10 +706,8 @@
           <t>SMRT1023</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>8908006537228</t>
-        </is>
+      <c r="G10" t="n">
+        <v>8908006537228</v>
       </c>
     </row>
     <row r="11">
@@ -760,10 +722,8 @@
       <c r="C11" t="n">
         <v>339</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D11" t="n">
+        <v>95030020</v>
       </c>
       <c r="E11" t="n">
         <v>0.05</v>
@@ -773,10 +733,8 @@
           <t>SMRT1024</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>8908006537235</t>
-        </is>
+      <c r="G11" t="n">
+        <v>8908006537235</v>
       </c>
     </row>
     <row r="12">
@@ -791,10 +749,8 @@
       <c r="C12" t="n">
         <v>339</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D12" t="n">
+        <v>95030020</v>
       </c>
       <c r="E12" t="n">
         <v>0.05</v>
@@ -804,10 +760,8 @@
           <t>SMRT1025</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8908006537242</t>
-        </is>
+      <c r="G12" t="n">
+        <v>8908006537242</v>
       </c>
     </row>
     <row r="13">
@@ -822,10 +776,8 @@
       <c r="C13" t="n">
         <v>339</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D13" t="n">
+        <v>95030020</v>
       </c>
       <c r="E13" t="n">
         <v>0.05</v>
@@ -835,10 +787,8 @@
           <t>SMRT1026</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>8908006537259</t>
-        </is>
+      <c r="G13" t="n">
+        <v>8908006537259</v>
       </c>
     </row>
     <row r="14">
@@ -853,10 +803,8 @@
       <c r="C14" t="n">
         <v>729</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D14" t="n">
+        <v>95030020</v>
       </c>
       <c r="E14" t="n">
         <v>0.05</v>
@@ -866,10 +814,8 @@
           <t>SMRT1027</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>8908006537266</t>
-        </is>
+      <c r="G14" t="n">
+        <v>8908006537266</v>
       </c>
     </row>
     <row r="15">
@@ -884,10 +830,8 @@
       <c r="C15" t="n">
         <v>1159</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D15" t="n">
+        <v>95030020</v>
       </c>
       <c r="E15" t="n">
         <v>0.05</v>
@@ -897,10 +841,8 @@
           <t>SMRT1028</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>8908006537273</t>
-        </is>
+      <c r="G15" t="n">
+        <v>8908006537273</v>
       </c>
     </row>
     <row r="16">
@@ -915,10 +857,8 @@
       <c r="C16" t="n">
         <v>1059</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D16" t="n">
+        <v>95030020</v>
       </c>
       <c r="E16" t="n">
         <v>0.05</v>
@@ -928,10 +868,8 @@
           <t>SMRT1031</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>8908006537303</t>
-        </is>
+      <c r="G16" t="n">
+        <v>8908006537303</v>
       </c>
     </row>
     <row r="17">
@@ -946,10 +884,8 @@
       <c r="C17" t="n">
         <v>1399</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D17" t="n">
+        <v>95030020</v>
       </c>
       <c r="E17" t="n">
         <v>0.05</v>
@@ -959,15 +895,11 @@
           <t>SMRT1032</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>8908006537310</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>8606924</t>
-        </is>
+      <c r="G17" t="n">
+        <v>8908006537310</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8606924</v>
       </c>
     </row>
     <row r="18">
@@ -982,10 +914,8 @@
       <c r="C18" t="n">
         <v>339</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D18" t="n">
+        <v>95030020</v>
       </c>
       <c r="E18" t="n">
         <v>0.05</v>
@@ -995,10 +925,8 @@
           <t>SMRT1033</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>8908006537327</t>
-        </is>
+      <c r="G18" t="n">
+        <v>8908006537327</v>
       </c>
     </row>
     <row r="19">
@@ -1013,10 +941,8 @@
       <c r="C19" t="n">
         <v>339</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D19" t="n">
+        <v>95030020</v>
       </c>
       <c r="E19" t="n">
         <v>0.05</v>
@@ -1026,10 +952,8 @@
           <t>SMRT1034</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>8908006537334</t>
-        </is>
+      <c r="G19" t="n">
+        <v>8908006537334</v>
       </c>
     </row>
     <row r="20">
@@ -1044,10 +968,8 @@
       <c r="C20" t="n">
         <v>339</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D20" t="n">
+        <v>95030020</v>
       </c>
       <c r="E20" t="n">
         <v>0.05</v>
@@ -1057,10 +979,8 @@
           <t>SMRT1035</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>8908006537341</t>
-        </is>
+      <c r="G20" t="n">
+        <v>8908006537341</v>
       </c>
     </row>
     <row r="21">
@@ -1075,10 +995,8 @@
       <c r="C21" t="n">
         <v>2229</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D21" t="n">
+        <v>95030020</v>
       </c>
       <c r="E21" t="n">
         <v>0.05</v>
@@ -1088,10 +1006,8 @@
           <t>SMRT1037</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>8908006537365</t>
-        </is>
+      <c r="G21" t="n">
+        <v>8908006537365</v>
       </c>
     </row>
     <row r="22">
@@ -1106,10 +1022,8 @@
       <c r="C22" t="n">
         <v>849</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D22" t="n">
+        <v>95030020</v>
       </c>
       <c r="E22" t="n">
         <v>0.05</v>
@@ -1119,15 +1033,11 @@
           <t>SMRT1040</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>8908006537396</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>61820</t>
-        </is>
+      <c r="G22" t="n">
+        <v>8908006537396</v>
+      </c>
+      <c r="I22" t="n">
+        <v>61820</v>
       </c>
     </row>
     <row r="23">
@@ -1142,10 +1052,8 @@
       <c r="C23" t="n">
         <v>869</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D23" t="n">
+        <v>95030020</v>
       </c>
       <c r="E23" t="n">
         <v>0.05</v>
@@ -1155,10 +1063,8 @@
           <t>SMRT1042</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>8908006537419</t>
-        </is>
+      <c r="G23" t="n">
+        <v>8908006537419</v>
       </c>
     </row>
     <row r="24">
@@ -1173,10 +1079,8 @@
       <c r="C24" t="n">
         <v>339</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D24" t="n">
+        <v>95030020</v>
       </c>
       <c r="E24" t="n">
         <v>0.05</v>
@@ -1186,10 +1090,8 @@
           <t>SMRT1043</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>8908006537426</t>
-        </is>
+      <c r="G24" t="n">
+        <v>8908006537426</v>
       </c>
     </row>
     <row r="25">
@@ -1204,10 +1106,8 @@
       <c r="C25" t="n">
         <v>339</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D25" t="n">
+        <v>95030020</v>
       </c>
       <c r="E25" t="n">
         <v>0.05</v>
@@ -1217,10 +1117,8 @@
           <t>SMRT1044</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>8908006537433</t>
-        </is>
+      <c r="G25" t="n">
+        <v>8908006537433</v>
       </c>
     </row>
     <row r="26">
@@ -1235,10 +1133,8 @@
       <c r="C26" t="n">
         <v>339</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D26" t="n">
+        <v>95030020</v>
       </c>
       <c r="E26" t="n">
         <v>0.05</v>
@@ -1248,10 +1144,8 @@
           <t>SMRT1045</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>8908006537440</t>
-        </is>
+      <c r="G26" t="n">
+        <v>8908006537440</v>
       </c>
     </row>
     <row r="27">
@@ -1266,10 +1160,8 @@
       <c r="C27" t="n">
         <v>339</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D27" t="n">
+        <v>95030020</v>
       </c>
       <c r="E27" t="n">
         <v>0.05</v>
@@ -1279,10 +1171,8 @@
           <t>SMRT1046</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>8908006537457</t>
-        </is>
+      <c r="G27" t="n">
+        <v>8908006537457</v>
       </c>
     </row>
     <row r="28">
@@ -1297,10 +1187,8 @@
       <c r="C28" t="n">
         <v>339</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D28" t="n">
+        <v>95030020</v>
       </c>
       <c r="E28" t="n">
         <v>0.05</v>
@@ -1310,10 +1198,8 @@
           <t>SMRT1047</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>8908006537464</t>
-        </is>
+      <c r="G28" t="n">
+        <v>8908006537464</v>
       </c>
     </row>
     <row r="29">
@@ -1328,10 +1214,8 @@
       <c r="C29" t="n">
         <v>769</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D29" t="n">
+        <v>95030020</v>
       </c>
       <c r="E29" t="n">
         <v>0.05</v>
@@ -1341,15 +1225,11 @@
           <t>SMRT1048</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>8908006537471</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>64139</t>
-        </is>
+      <c r="G29" t="n">
+        <v>8908006537471</v>
+      </c>
+      <c r="I29" t="n">
+        <v>64139</v>
       </c>
     </row>
     <row r="30">
@@ -1364,10 +1244,8 @@
       <c r="C30" t="n">
         <v>679</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D30" t="n">
+        <v>95030020</v>
       </c>
       <c r="E30" t="n">
         <v>0.05</v>
@@ -1377,10 +1255,8 @@
           <t>SMRT1049</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>8908006537488</t>
-        </is>
+      <c r="G30" t="n">
+        <v>8908006537488</v>
       </c>
     </row>
     <row r="31">
@@ -1395,10 +1271,8 @@
       <c r="C31" t="n">
         <v>679</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D31" t="n">
+        <v>95030020</v>
       </c>
       <c r="E31" t="n">
         <v>0.05</v>
@@ -1408,10 +1282,8 @@
           <t>SMRT1050</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>8908006537501</t>
-        </is>
+      <c r="G31" t="n">
+        <v>8908006537501</v>
       </c>
     </row>
     <row r="32">
@@ -1426,10 +1298,8 @@
       <c r="C32" t="n">
         <v>1059</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D32" t="n">
+        <v>95030020</v>
       </c>
       <c r="E32" t="n">
         <v>0.05</v>
@@ -1439,10 +1309,8 @@
           <t>SMRT1055</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>8908006537556</t>
-        </is>
+      <c r="G32" t="n">
+        <v>8908006537556</v>
       </c>
     </row>
     <row r="33">
@@ -1457,10 +1325,8 @@
       <c r="C33" t="n">
         <v>1899</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>95030010</t>
-        </is>
+      <c r="D33" t="n">
+        <v>95030010</v>
       </c>
       <c r="E33" t="n">
         <v>0.18</v>
@@ -1470,10 +1336,8 @@
           <t>SMRT1057</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>8908006537570</t>
-        </is>
+      <c r="G33" t="n">
+        <v>8908006537570</v>
       </c>
     </row>
     <row r="34">
@@ -1488,10 +1352,8 @@
       <c r="C34" t="n">
         <v>4999</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>95030010</t>
-        </is>
+      <c r="D34" t="n">
+        <v>95030010</v>
       </c>
       <c r="E34" t="n">
         <v>0.18</v>
@@ -1501,10 +1363,8 @@
           <t>SMRT1068</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>8908006537631</t>
-        </is>
+      <c r="G34" t="n">
+        <v>8908006537631</v>
       </c>
     </row>
     <row r="35">
@@ -1519,10 +1379,8 @@
       <c r="C35" t="n">
         <v>1159</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D35" t="n">
+        <v>95030020</v>
       </c>
       <c r="E35" t="n">
         <v>0.05</v>
@@ -1532,10 +1390,8 @@
           <t>SMRT1076</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>8908006537716</t>
-        </is>
+      <c r="G35" t="n">
+        <v>8908006537716</v>
       </c>
     </row>
     <row r="36">
@@ -1550,10 +1406,8 @@
       <c r="C36" t="n">
         <v>1159</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D36" t="n">
+        <v>95030020</v>
       </c>
       <c r="E36" t="n">
         <v>0.05</v>
@@ -1563,10 +1417,8 @@
           <t>SMRT1077</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>8908006537723</t>
-        </is>
+      <c r="G36" t="n">
+        <v>8908006537723</v>
       </c>
     </row>
     <row r="37">
@@ -1581,10 +1433,8 @@
       <c r="C37" t="n">
         <v>969</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D37" t="n">
+        <v>95030020</v>
       </c>
       <c r="E37" t="n">
         <v>0.05</v>
@@ -1594,10 +1444,8 @@
           <t>SMRT1078</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>8908006537730</t>
-        </is>
+      <c r="G37" t="n">
+        <v>8908006537730</v>
       </c>
     </row>
     <row r="38">
@@ -1612,10 +1460,8 @@
       <c r="C38" t="n">
         <v>159</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D38" t="n">
+        <v>95030020</v>
       </c>
       <c r="E38" t="n">
         <v>0.05</v>
@@ -1625,10 +1471,8 @@
           <t>SMRT1082</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>8908006537778</t>
-        </is>
+      <c r="G38" t="n">
+        <v>8908006537778</v>
       </c>
     </row>
     <row r="39">
@@ -1643,10 +1487,8 @@
       <c r="C39" t="n">
         <v>159</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D39" t="n">
+        <v>95030020</v>
       </c>
       <c r="E39" t="n">
         <v>0.05</v>
@@ -1656,10 +1498,8 @@
           <t>SMRT1083</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>8908006537785</t>
-        </is>
+      <c r="G39" t="n">
+        <v>8908006537785</v>
       </c>
     </row>
     <row r="40">
@@ -1674,10 +1514,8 @@
       <c r="C40" t="n">
         <v>159</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D40" t="n">
+        <v>95030020</v>
       </c>
       <c r="E40" t="n">
         <v>0.05</v>
@@ -1687,10 +1525,8 @@
           <t>SMRT1084</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>8908006537792</t>
-        </is>
+      <c r="G40" t="n">
+        <v>8908006537792</v>
       </c>
     </row>
     <row r="41">
@@ -1705,10 +1541,8 @@
       <c r="C41" t="n">
         <v>159</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D41" t="n">
+        <v>95030020</v>
       </c>
       <c r="E41" t="n">
         <v>0.05</v>
@@ -1718,10 +1552,8 @@
           <t>SMRT1085</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>8908006537808</t>
-        </is>
+      <c r="G41" t="n">
+        <v>8908006537808</v>
       </c>
     </row>
     <row r="42">
@@ -1736,10 +1568,8 @@
       <c r="C42" t="n">
         <v>159</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D42" t="n">
+        <v>95030020</v>
       </c>
       <c r="E42" t="n">
         <v>0.05</v>
@@ -1749,10 +1579,8 @@
           <t>SMRT1086</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>8908006537815</t>
-        </is>
+      <c r="G42" t="n">
+        <v>8908006537815</v>
       </c>
     </row>
     <row r="43">
@@ -1767,10 +1595,8 @@
       <c r="C43" t="n">
         <v>159</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D43" t="n">
+        <v>95030020</v>
       </c>
       <c r="E43" t="n">
         <v>0.05</v>
@@ -1780,10 +1606,8 @@
           <t>SMRT1087</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>8908006537822</t>
-        </is>
+      <c r="G43" t="n">
+        <v>8908006537822</v>
       </c>
     </row>
     <row r="44">
@@ -1798,10 +1622,8 @@
       <c r="C44" t="n">
         <v>629</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D44" t="n">
+        <v>95030020</v>
       </c>
       <c r="E44" t="n">
         <v>0.05</v>
@@ -1811,10 +1633,8 @@
           <t>SMRT1090</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>8908006537853</t>
-        </is>
+      <c r="G44" t="n">
+        <v>8908006537853</v>
       </c>
     </row>
     <row r="45">
@@ -1829,10 +1649,8 @@
       <c r="C45" t="n">
         <v>159</v>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D45" t="n">
+        <v>95030020</v>
       </c>
       <c r="E45" t="n">
         <v>0.05</v>
@@ -1842,10 +1660,8 @@
           <t>SMRT1091</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>8908006537860</t>
-        </is>
+      <c r="G45" t="n">
+        <v>8908006537860</v>
       </c>
     </row>
     <row r="46">
@@ -1860,10 +1676,8 @@
       <c r="C46" t="n">
         <v>159</v>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D46" t="n">
+        <v>95030020</v>
       </c>
       <c r="E46" t="n">
         <v>0.05</v>
@@ -1873,10 +1687,8 @@
           <t>SMRT1092</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>8908006537877</t>
-        </is>
+      <c r="G46" t="n">
+        <v>8908006537877</v>
       </c>
     </row>
     <row r="47">
@@ -1891,10 +1703,8 @@
       <c r="C47" t="n">
         <v>159</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D47" t="n">
+        <v>95030020</v>
       </c>
       <c r="E47" t="n">
         <v>0.05</v>
@@ -1904,10 +1714,8 @@
           <t>SMRT1093</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>8908006537884</t>
-        </is>
+      <c r="G47" t="n">
+        <v>8908006537884</v>
       </c>
     </row>
     <row r="48">
@@ -1922,10 +1730,8 @@
       <c r="C48" t="n">
         <v>529</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D48" t="n">
+        <v>95030020</v>
       </c>
       <c r="E48" t="n">
         <v>0.05</v>
@@ -1935,15 +1741,11 @@
           <t>SMRT1098</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>8908006537907</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>8606931</t>
-        </is>
+      <c r="G48" t="n">
+        <v>8908006537907</v>
+      </c>
+      <c r="H48" t="n">
+        <v>8606931</v>
       </c>
     </row>
     <row r="49">
@@ -1958,10 +1760,8 @@
       <c r="C49" t="n">
         <v>869</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D49" t="n">
+        <v>95030020</v>
       </c>
       <c r="E49" t="n">
         <v>0.05</v>
@@ -1971,10 +1771,8 @@
           <t>SMRT1099</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>8908006537914</t>
-        </is>
+      <c r="G49" t="n">
+        <v>8908006537914</v>
       </c>
     </row>
     <row r="50">
@@ -1989,10 +1787,8 @@
       <c r="C50" t="n">
         <v>1059</v>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D50" t="n">
+        <v>95030020</v>
       </c>
       <c r="E50" t="n">
         <v>0.05</v>
@@ -2002,10 +1798,8 @@
           <t>SMRT1101</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>8908006537921</t>
-        </is>
+      <c r="G50" t="n">
+        <v>8908006537921</v>
       </c>
     </row>
     <row r="51">
@@ -2020,10 +1814,8 @@
       <c r="C51" t="n">
         <v>379</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D51" t="n">
+        <v>95030020</v>
       </c>
       <c r="E51" t="n">
         <v>0.05</v>
@@ -2033,10 +1825,8 @@
           <t>SMRT1107</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>8908006537983</t>
-        </is>
+      <c r="G51" t="n">
+        <v>8908006537983</v>
       </c>
     </row>
     <row r="52">
@@ -2051,10 +1841,8 @@
       <c r="C52" t="n">
         <v>379</v>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D52" t="n">
+        <v>95030020</v>
       </c>
       <c r="E52" t="n">
         <v>0.05</v>
@@ -2064,10 +1852,8 @@
           <t>SMRT1108</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>8908006537990</t>
-        </is>
+      <c r="G52" t="n">
+        <v>8908006537990</v>
       </c>
     </row>
     <row r="53">
@@ -2082,10 +1868,8 @@
       <c r="C53" t="n">
         <v>549</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D53" t="n">
+        <v>95030020</v>
       </c>
       <c r="E53" t="n">
         <v>0.05</v>
@@ -2095,20 +1879,14 @@
           <t>SMRT1109(V6)</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>8908006537297</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>8606935</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>91537</t>
-        </is>
+      <c r="G53" t="n">
+        <v>8908006537297</v>
+      </c>
+      <c r="H53" t="n">
+        <v>8606935</v>
+      </c>
+      <c r="I53" t="n">
+        <v>91537</v>
       </c>
     </row>
     <row r="54">
@@ -2123,10 +1901,8 @@
       <c r="C54" t="n">
         <v>379</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D54" t="n">
+        <v>95030020</v>
       </c>
       <c r="E54" t="n">
         <v>0.05</v>
@@ -2136,10 +1912,8 @@
           <t>SMRT1110</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>8908006537389</t>
-        </is>
+      <c r="G54" t="n">
+        <v>8908006537389</v>
       </c>
     </row>
     <row r="55">
@@ -2154,10 +1928,8 @@
       <c r="C55" t="n">
         <v>629</v>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D55" t="n">
+        <v>95030020</v>
       </c>
       <c r="E55" t="n">
         <v>0.05</v>
@@ -2167,10 +1939,8 @@
           <t>SMRT1112</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>8908006537549</t>
-        </is>
+      <c r="G55" t="n">
+        <v>8908006537549</v>
       </c>
     </row>
     <row r="56">
@@ -2185,10 +1955,8 @@
       <c r="C56" t="n">
         <v>1159</v>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D56" t="n">
+        <v>95030020</v>
       </c>
       <c r="E56" t="n">
         <v>0.05</v>
@@ -2198,10 +1966,8 @@
           <t>SMRT1113</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>8908006537372</t>
-        </is>
+      <c r="G56" t="n">
+        <v>8908006537372</v>
       </c>
     </row>
     <row r="57">
@@ -2216,10 +1982,8 @@
       <c r="C57" t="n">
         <v>1259</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D57" t="n">
+        <v>95030020</v>
       </c>
       <c r="E57" t="n">
         <v>0.05</v>
@@ -2229,10 +1993,8 @@
           <t>SMRT1117</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>8908006537969</t>
-        </is>
+      <c r="G57" t="n">
+        <v>8908006537969</v>
       </c>
     </row>
     <row r="58">
@@ -2247,10 +2009,8 @@
       <c r="C58" t="n">
         <v>1159</v>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D58" t="n">
+        <v>95030020</v>
       </c>
       <c r="E58" t="n">
         <v>0.05</v>
@@ -2260,10 +2020,8 @@
           <t>SMRT1118</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>8908006537976</t>
-        </is>
+      <c r="G58" t="n">
+        <v>8908006537976</v>
       </c>
     </row>
     <row r="59">
@@ -2278,10 +2036,8 @@
       <c r="C59" t="n">
         <v>1159</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D59" t="n">
+        <v>95030020</v>
       </c>
       <c r="E59" t="n">
         <v>0.05</v>
@@ -2291,10 +2047,8 @@
           <t>SMRT1124</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>8908011797020</t>
-        </is>
+      <c r="G59" t="n">
+        <v>8908011797020</v>
       </c>
     </row>
     <row r="60">
@@ -2309,10 +2063,8 @@
       <c r="C60" t="n">
         <v>1159</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D60" t="n">
+        <v>95030020</v>
       </c>
       <c r="E60" t="n">
         <v>0.05</v>
@@ -2322,10 +2074,8 @@
           <t>SMRT1125</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>8908011797037</t>
-        </is>
+      <c r="G60" t="n">
+        <v>8908011797037</v>
       </c>
     </row>
     <row r="61">
@@ -2340,10 +2090,8 @@
       <c r="C61" t="n">
         <v>629</v>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D61" t="n">
+        <v>95030020</v>
       </c>
       <c r="E61" t="n">
         <v>0.05</v>
@@ -2353,10 +2101,8 @@
           <t>SMRT1128</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>8908011797051</t>
-        </is>
+      <c r="G61" t="n">
+        <v>8908011797051</v>
       </c>
     </row>
     <row r="62">
@@ -2371,10 +2117,8 @@
       <c r="C62" t="n">
         <v>869</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D62" t="n">
+        <v>95030020</v>
       </c>
       <c r="E62" t="n">
         <v>0.05</v>
@@ -2384,10 +2128,8 @@
           <t>SMRT1130</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>8908011797075</t>
-        </is>
+      <c r="G62" t="n">
+        <v>8908011797075</v>
       </c>
     </row>
     <row r="63">
@@ -2402,10 +2144,8 @@
       <c r="C63" t="n">
         <v>1259</v>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D63" t="n">
+        <v>95030020</v>
       </c>
       <c r="E63" t="n">
         <v>0.05</v>
@@ -2415,10 +2155,8 @@
           <t>SMRT1131</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>8908011797068</t>
-        </is>
+      <c r="G63" t="n">
+        <v>8908011797068</v>
       </c>
     </row>
     <row r="64">
@@ -2433,10 +2171,8 @@
       <c r="C64" t="n">
         <v>1999</v>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>95030010</t>
-        </is>
+      <c r="D64" t="n">
+        <v>95030010</v>
       </c>
       <c r="E64" t="n">
         <v>0.18</v>
@@ -2446,10 +2182,8 @@
           <t>SMRT1132</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>8908011797136</t>
-        </is>
+      <c r="G64" t="n">
+        <v>8908011797136</v>
       </c>
     </row>
     <row r="65">
@@ -2464,10 +2198,8 @@
       <c r="C65" t="n">
         <v>1059</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D65" t="n">
+        <v>95030020</v>
       </c>
       <c r="E65" t="n">
         <v>0.05</v>
@@ -2477,10 +2209,8 @@
           <t>SMRT1134</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>8908011797082</t>
-        </is>
+      <c r="G65" t="n">
+        <v>8908011797082</v>
       </c>
     </row>
     <row r="66">
@@ -2495,10 +2225,8 @@
       <c r="C66" t="n">
         <v>1249</v>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D66" t="n">
+        <v>95030020</v>
       </c>
       <c r="E66" t="n">
         <v>0.05</v>
@@ -2508,20 +2236,14 @@
           <t>SMRT1135</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>8908011797099</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>8606950</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>51344</t>
-        </is>
+      <c r="G66" t="n">
+        <v>8908011797099</v>
+      </c>
+      <c r="H66" t="n">
+        <v>8606950</v>
+      </c>
+      <c r="I66" t="n">
+        <v>51344</v>
       </c>
     </row>
     <row r="67">
@@ -2536,10 +2258,8 @@
       <c r="C67" t="n">
         <v>1259</v>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>95030010</t>
-        </is>
+      <c r="D67" t="n">
+        <v>95030010</v>
       </c>
       <c r="E67" t="n">
         <v>0.18</v>
@@ -2549,20 +2269,14 @@
           <t>SMRT1139-18</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>8908011797105</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>8606952</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>56867</t>
-        </is>
+      <c r="G67" t="n">
+        <v>8908011797105</v>
+      </c>
+      <c r="H67" t="n">
+        <v>8606952</v>
+      </c>
+      <c r="I67" t="n">
+        <v>56867</v>
       </c>
     </row>
     <row r="68">
@@ -2577,10 +2291,8 @@
       <c r="C68" t="n">
         <v>979</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D68" t="n">
+        <v>95030020</v>
       </c>
       <c r="E68" t="n">
         <v>0.05</v>
@@ -2590,20 +2302,14 @@
           <t>SMRT1163(V3)</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>8908011797143</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>8947269</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>73783</t>
-        </is>
+      <c r="G68" t="n">
+        <v>8908011797143</v>
+      </c>
+      <c r="H68" t="n">
+        <v>8947269</v>
+      </c>
+      <c r="I68" t="n">
+        <v>73783</v>
       </c>
     </row>
     <row r="69">
@@ -2618,10 +2324,8 @@
       <c r="C69" t="n">
         <v>1549</v>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D69" t="n">
+        <v>95030020</v>
       </c>
       <c r="E69" t="n">
         <v>0.05</v>
@@ -2631,15 +2335,11 @@
           <t>SMRT1165</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>8908011797150</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>8947250</t>
-        </is>
+      <c r="G69" t="n">
+        <v>8908011797150</v>
+      </c>
+      <c r="H69" t="n">
+        <v>8947250</v>
       </c>
     </row>
     <row r="70">
@@ -2654,10 +2354,8 @@
       <c r="C70" t="n">
         <v>3879</v>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D70" t="n">
+        <v>95030020</v>
       </c>
       <c r="E70" t="n">
         <v>0.05</v>
@@ -2667,10 +2365,8 @@
           <t>SMRT1168</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>8908011797129</t>
-        </is>
+      <c r="G70" t="n">
+        <v>8908011797129</v>
       </c>
     </row>
     <row r="71">
@@ -2685,10 +2381,8 @@
       <c r="C71" t="n">
         <v>1599</v>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D71" t="n">
+        <v>95030020</v>
       </c>
       <c r="E71" t="n">
         <v>0.05</v>
@@ -2698,20 +2392,14 @@
           <t>SMRT1169</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>8908011797204</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>8947251</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>93878</t>
-        </is>
+      <c r="G71" t="n">
+        <v>8908011797204</v>
+      </c>
+      <c r="H71" t="n">
+        <v>8947251</v>
+      </c>
+      <c r="I71" t="n">
+        <v>93878</v>
       </c>
     </row>
     <row r="72">
@@ -2726,10 +2414,8 @@
       <c r="C72" t="n">
         <v>849</v>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D72" t="n">
+        <v>95030020</v>
       </c>
       <c r="E72" t="n">
         <v>0.05</v>
@@ -2739,20 +2425,14 @@
           <t>SMRT1174</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>8908011797211</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>8947249</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>97450</t>
-        </is>
+      <c r="G72" t="n">
+        <v>8908011797211</v>
+      </c>
+      <c r="H72" t="n">
+        <v>8947249</v>
+      </c>
+      <c r="I72" t="n">
+        <v>97450</v>
       </c>
     </row>
     <row r="73">
@@ -2767,10 +2447,8 @@
       <c r="C73" t="n">
         <v>669</v>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D73" t="n">
+        <v>95030020</v>
       </c>
       <c r="E73" t="n">
         <v>0.05</v>
@@ -2780,10 +2458,8 @@
           <t>SMRT1175</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>8908011797167</t>
-        </is>
+      <c r="G73" t="n">
+        <v>8908011797167</v>
       </c>
     </row>
     <row r="74">
@@ -2798,10 +2474,8 @@
       <c r="C74" t="n">
         <v>669</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D74" t="n">
+        <v>95030020</v>
       </c>
       <c r="E74" t="n">
         <v>0.05</v>
@@ -2811,10 +2485,8 @@
           <t>SMRT1176</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>8908011797174</t>
-        </is>
+      <c r="G74" t="n">
+        <v>8908011797174</v>
       </c>
     </row>
     <row r="75">
@@ -2829,10 +2501,8 @@
       <c r="C75" t="n">
         <v>669</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D75" t="n">
+        <v>95030020</v>
       </c>
       <c r="E75" t="n">
         <v>0.05</v>
@@ -2842,10 +2512,8 @@
           <t>SMRT1177</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>8908011797181</t>
-        </is>
+      <c r="G75" t="n">
+        <v>8908011797181</v>
       </c>
     </row>
     <row r="76">
@@ -2860,10 +2528,8 @@
       <c r="C76" t="n">
         <v>669</v>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D76" t="n">
+        <v>95030020</v>
       </c>
       <c r="E76" t="n">
         <v>0.05</v>
@@ -2873,10 +2539,8 @@
           <t>SMRT1178</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>8908011797198</t>
-        </is>
+      <c r="G76" t="n">
+        <v>8908011797198</v>
       </c>
     </row>
     <row r="77">
@@ -2891,10 +2555,8 @@
       <c r="C77" t="n">
         <v>1099</v>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D77" t="n">
+        <v>95030020</v>
       </c>
       <c r="E77" t="n">
         <v>0.05</v>
@@ -2904,20 +2566,14 @@
           <t>SMRT1179</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>8908011797228</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>13353538</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>75870</t>
-        </is>
+      <c r="G77" t="n">
+        <v>8908011797228</v>
+      </c>
+      <c r="H77" t="n">
+        <v>13353538</v>
+      </c>
+      <c r="I77" t="n">
+        <v>75870</v>
       </c>
     </row>
     <row r="78">
@@ -2932,10 +2588,8 @@
       <c r="C78" t="n">
         <v>769</v>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D78" t="n">
+        <v>95030020</v>
       </c>
       <c r="E78" t="n">
         <v>0.05</v>
@@ -2945,10 +2599,8 @@
           <t>SMRT1180</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>8908011797242</t>
-        </is>
+      <c r="G78" t="n">
+        <v>8908011797242</v>
       </c>
     </row>
     <row r="79">
@@ -2963,10 +2615,8 @@
       <c r="C79" t="n">
         <v>819</v>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D79" t="n">
+        <v>95030020</v>
       </c>
       <c r="E79" t="n">
         <v>0.05</v>
@@ -2976,10 +2626,8 @@
           <t>SMRT1181</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>8908011797273</t>
-        </is>
+      <c r="G79" t="n">
+        <v>8908011797273</v>
       </c>
     </row>
     <row r="80">
@@ -2994,10 +2642,8 @@
       <c r="C80" t="n">
         <v>1299</v>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D80" t="n">
+        <v>95030020</v>
       </c>
       <c r="E80" t="n">
         <v>0.05</v>
@@ -3007,20 +2653,14 @@
           <t>SMRT1182</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>8908011797297</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>10127435</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>85666</t>
-        </is>
+      <c r="G80" t="n">
+        <v>8908011797297</v>
+      </c>
+      <c r="H80" t="n">
+        <v>10127435</v>
+      </c>
+      <c r="I80" t="n">
+        <v>85666</v>
       </c>
     </row>
     <row r="81">
@@ -3035,10 +2675,8 @@
       <c r="C81" t="n">
         <v>919</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D81" t="n">
+        <v>95030020</v>
       </c>
       <c r="E81" t="n">
         <v>0.05</v>
@@ -3048,10 +2686,8 @@
           <t>SMRT1183</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>8908011797280</t>
-        </is>
+      <c r="G81" t="n">
+        <v>8908011797280</v>
       </c>
     </row>
     <row r="82">
@@ -3066,10 +2702,8 @@
       <c r="C82" t="n">
         <v>1159</v>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D82" t="n">
+        <v>95030020</v>
       </c>
       <c r="E82" t="n">
         <v>0.05</v>
@@ -3079,20 +2713,14 @@
           <t>SMRT1184</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>8908011797327</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>13353535</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>65810</t>
-        </is>
+      <c r="G82" t="n">
+        <v>8908011797327</v>
+      </c>
+      <c r="H82" t="n">
+        <v>13353535</v>
+      </c>
+      <c r="I82" t="n">
+        <v>65810</v>
       </c>
     </row>
     <row r="83">
@@ -3107,10 +2735,8 @@
       <c r="C83" t="n">
         <v>869</v>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D83" t="n">
+        <v>95030020</v>
       </c>
       <c r="E83" t="n">
         <v>0.05</v>
@@ -3120,10 +2746,8 @@
           <t>SMRT1186</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>8908011797235</t>
-        </is>
+      <c r="G83" t="n">
+        <v>8908011797235</v>
       </c>
     </row>
     <row r="84">
@@ -3138,10 +2762,8 @@
       <c r="C84" t="n">
         <v>819</v>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D84" t="n">
+        <v>95030020</v>
       </c>
       <c r="E84" t="n">
         <v>0.05</v>
@@ -3151,10 +2773,8 @@
           <t>SMRT1187</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>8908011797266</t>
-        </is>
+      <c r="G84" t="n">
+        <v>8908011797266</v>
       </c>
     </row>
     <row r="85">
@@ -3169,10 +2789,8 @@
       <c r="C85" t="n">
         <v>868</v>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D85" t="n">
+        <v>95030020</v>
       </c>
       <c r="E85" t="n">
         <v>0.05</v>
@@ -3182,10 +2800,8 @@
           <t>SMRT1188</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>8908011797310</t>
-        </is>
+      <c r="G85" t="n">
+        <v>8908011797310</v>
       </c>
     </row>
     <row r="86">
@@ -3200,10 +2816,8 @@
       <c r="C86" t="n">
         <v>869</v>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D86" t="n">
+        <v>95030020</v>
       </c>
       <c r="E86" t="n">
         <v>0.05</v>
@@ -3213,10 +2827,8 @@
           <t>SMRT1189</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>8908011797334</t>
-        </is>
+      <c r="G86" t="n">
+        <v>8908011797334</v>
       </c>
     </row>
     <row r="87">
@@ -3231,10 +2843,8 @@
       <c r="C87" t="n">
         <v>1059</v>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D87" t="n">
+        <v>95030020</v>
       </c>
       <c r="E87" t="n">
         <v>0.05</v>
@@ -3244,10 +2854,8 @@
           <t>SMRT1190</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>8908011797426</t>
-        </is>
+      <c r="G87" t="n">
+        <v>8908011797426</v>
       </c>
     </row>
     <row r="88">
@@ -3262,10 +2870,8 @@
       <c r="C88" t="n">
         <v>869</v>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D88" t="n">
+        <v>95030020</v>
       </c>
       <c r="E88" t="n">
         <v>0.05</v>
@@ -3275,20 +2881,14 @@
           <t>SMRT1191</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>8908006537563</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>10712380</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>74823</t>
-        </is>
+      <c r="G88" t="n">
+        <v>8908006537563</v>
+      </c>
+      <c r="H88" t="n">
+        <v>10712380</v>
+      </c>
+      <c r="I88" t="n">
+        <v>74823</v>
       </c>
     </row>
     <row r="89">
@@ -3303,10 +2903,8 @@
       <c r="C89" t="n">
         <v>1099</v>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D89" t="n">
+        <v>95030020</v>
       </c>
       <c r="E89" t="n">
         <v>0.05</v>
@@ -3316,20 +2914,14 @@
           <t>SMRT1192</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>8908011797303</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>10127433</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>79024</t>
-        </is>
+      <c r="G89" t="n">
+        <v>8908011797303</v>
+      </c>
+      <c r="H89" t="n">
+        <v>10127433</v>
+      </c>
+      <c r="I89" t="n">
+        <v>79024</v>
       </c>
     </row>
     <row r="90">
@@ -3344,10 +2936,8 @@
       <c r="C90" t="n">
         <v>1059</v>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D90" t="n">
+        <v>95030020</v>
       </c>
       <c r="E90" t="n">
         <v>0.05</v>
@@ -3357,10 +2947,8 @@
           <t>SMRT1197</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>8908006537587</t>
-        </is>
+      <c r="G90" t="n">
+        <v>8908006537587</v>
       </c>
     </row>
     <row r="91">
@@ -3375,10 +2963,8 @@
       <c r="C91" t="n">
         <v>869</v>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D91" t="n">
+        <v>95030020</v>
       </c>
       <c r="E91" t="n">
         <v>0.05</v>
@@ -3388,10 +2974,8 @@
           <t>SMRT1204</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>8908006537594</t>
-        </is>
+      <c r="G91" t="n">
+        <v>8908006537594</v>
       </c>
     </row>
     <row r="92">
@@ -3406,10 +2990,8 @@
       <c r="C92" t="n">
         <v>869</v>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D92" t="n">
+        <v>95030020</v>
       </c>
       <c r="E92" t="n">
         <v>0.05</v>
@@ -3419,10 +3001,8 @@
           <t>SMRT1206</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>8908006537709</t>
-        </is>
+      <c r="G92" t="n">
+        <v>8908006537709</v>
       </c>
     </row>
     <row r="93">
@@ -3437,10 +3017,8 @@
       <c r="C93" t="n">
         <v>819</v>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D93" t="n">
+        <v>95030020</v>
       </c>
       <c r="E93" t="n">
         <v>0.05</v>
@@ -3450,10 +3028,8 @@
           <t>SMRT1209</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>8908011797471</t>
-        </is>
+      <c r="G93" t="n">
+        <v>8908011797471</v>
       </c>
     </row>
     <row r="94">
@@ -3468,10 +3044,8 @@
       <c r="C94" t="n">
         <v>1099</v>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>95030010</t>
-        </is>
+      <c r="D94" t="n">
+        <v>95030010</v>
       </c>
       <c r="E94" t="n">
         <v>0.18</v>
@@ -3481,20 +3055,14 @@
           <t>SMRT1214-18</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>8908011797488</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>13353534</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>70537</t>
-        </is>
+      <c r="G94" t="n">
+        <v>8908011797488</v>
+      </c>
+      <c r="H94" t="n">
+        <v>13353534</v>
+      </c>
+      <c r="I94" t="n">
+        <v>70537</v>
       </c>
     </row>
     <row r="95">
@@ -3509,10 +3077,8 @@
       <c r="C95" t="n">
         <v>1059</v>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D95" t="n">
+        <v>95030020</v>
       </c>
       <c r="E95" t="n">
         <v>0.05</v>
@@ -3522,15 +3088,11 @@
           <t>SMRT1215(V2)</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>8908011797464</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>481367</t>
-        </is>
+      <c r="G95" t="n">
+        <v>8908011797464</v>
+      </c>
+      <c r="I95" t="n">
+        <v>481367</v>
       </c>
     </row>
     <row r="96">
@@ -3545,10 +3107,8 @@
       <c r="C96" t="n">
         <v>1399</v>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>95030010</t>
-        </is>
+      <c r="D96" t="n">
+        <v>95030010</v>
       </c>
       <c r="E96" t="n">
         <v>0.18</v>
@@ -3558,20 +3118,14 @@
           <t>SMRT1216</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>8908011797518</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>13353529</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>86497</t>
-        </is>
+      <c r="G96" t="n">
+        <v>8908011797518</v>
+      </c>
+      <c r="H96" t="n">
+        <v>13353529</v>
+      </c>
+      <c r="I96" t="n">
+        <v>86497</v>
       </c>
     </row>
     <row r="97">
@@ -3586,10 +3140,8 @@
       <c r="C97" t="n">
         <v>819</v>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D97" t="n">
+        <v>95030020</v>
       </c>
       <c r="E97" t="n">
         <v>0.05</v>
@@ -3599,10 +3151,8 @@
           <t>SMRT1220</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>8908011797570</t>
-        </is>
+      <c r="G97" t="n">
+        <v>8908011797570</v>
       </c>
     </row>
     <row r="98">
@@ -3617,10 +3167,8 @@
       <c r="C98" t="n">
         <v>1159</v>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D98" t="n">
+        <v>95030020</v>
       </c>
       <c r="E98" t="n">
         <v>0.05</v>
@@ -3630,10 +3178,8 @@
           <t>SMRT1221(V2)</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>8908011797792</t>
-        </is>
+      <c r="G98" t="n">
+        <v>8908011797792</v>
       </c>
     </row>
     <row r="99">
@@ -3648,10 +3194,8 @@
       <c r="C99" t="n">
         <v>969</v>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D99" t="n">
+        <v>95030020</v>
       </c>
       <c r="E99" t="n">
         <v>0.05</v>
@@ -3661,20 +3205,14 @@
           <t>SMRT1222</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>8908011797549</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>13353532</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>96340</t>
-        </is>
+      <c r="G99" t="n">
+        <v>8908011797549</v>
+      </c>
+      <c r="H99" t="n">
+        <v>13353532</v>
+      </c>
+      <c r="I99" t="n">
+        <v>96340</v>
       </c>
     </row>
     <row r="100">
@@ -3689,10 +3227,8 @@
       <c r="C100" t="n">
         <v>869</v>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D100" t="n">
+        <v>95030020</v>
       </c>
       <c r="E100" t="n">
         <v>0.05</v>
@@ -3702,10 +3238,8 @@
           <t>SMRT1223</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>8908011797532</t>
-        </is>
+      <c r="G100" t="n">
+        <v>8908011797532</v>
       </c>
     </row>
     <row r="101">
@@ -3720,10 +3254,8 @@
       <c r="C101" t="n">
         <v>969</v>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D101" t="n">
+        <v>95030020</v>
       </c>
       <c r="E101" t="n">
         <v>0.05</v>
@@ -3733,10 +3265,8 @@
           <t>SMRT1226</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>8908011797563</t>
-        </is>
+      <c r="G101" t="n">
+        <v>8908011797563</v>
       </c>
     </row>
     <row r="102">
@@ -3751,10 +3281,8 @@
       <c r="C102" t="n">
         <v>1739</v>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D102" t="n">
+        <v>95030020</v>
       </c>
       <c r="E102" t="n">
         <v>0.05</v>
@@ -3764,10 +3292,8 @@
           <t>SMRT1227</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>8908011797556</t>
-        </is>
+      <c r="G102" t="n">
+        <v>8908011797556</v>
       </c>
     </row>
     <row r="103">
@@ -3782,10 +3308,8 @@
       <c r="C103" t="n">
         <v>869</v>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D103" t="n">
+        <v>95030020</v>
       </c>
       <c r="E103" t="n">
         <v>0.05</v>
@@ -3795,10 +3319,8 @@
           <t>SMRT1228</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>8908011797587</t>
-        </is>
+      <c r="G103" t="n">
+        <v>8908011797587</v>
       </c>
     </row>
     <row r="104">
@@ -3813,10 +3335,8 @@
       <c r="C104" t="n">
         <v>1099</v>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>95030010</t>
-        </is>
+      <c r="D104" t="n">
+        <v>95030010</v>
       </c>
       <c r="E104" t="n">
         <v>0.18</v>
@@ -3826,20 +3346,14 @@
           <t>SMRT1230-18</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>8908011797600</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>13694135</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>73466</t>
-        </is>
+      <c r="G104" t="n">
+        <v>8908011797600</v>
+      </c>
+      <c r="H104" t="n">
+        <v>13694135</v>
+      </c>
+      <c r="I104" t="n">
+        <v>73466</v>
       </c>
     </row>
     <row r="105">
@@ -3854,10 +3368,8 @@
       <c r="C105" t="n">
         <v>1299</v>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D105" t="n">
+        <v>95030020</v>
       </c>
       <c r="E105" t="n">
         <v>0.05</v>
@@ -3867,10 +3379,8 @@
           <t>SMRT1233</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>8908011797617</t>
-        </is>
+      <c r="G105" t="n">
+        <v>8908011797617</v>
       </c>
     </row>
     <row r="106">
@@ -3885,10 +3395,8 @@
       <c r="C106" t="n">
         <v>999</v>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D106" t="n">
+        <v>95030020</v>
       </c>
       <c r="E106" t="n">
         <v>0.05</v>
@@ -3898,15 +3406,11 @@
           <t>SMRT1236</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>8908011797648</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>458614</t>
-        </is>
+      <c r="G106" t="n">
+        <v>8908011797648</v>
+      </c>
+      <c r="I106" t="n">
+        <v>458614</v>
       </c>
     </row>
     <row r="107">
@@ -3921,10 +3425,8 @@
       <c r="C107" t="n">
         <v>1099</v>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D107" t="n">
+        <v>95030020</v>
       </c>
       <c r="E107" t="n">
         <v>0.05</v>
@@ -3934,15 +3436,11 @@
           <t>SMRT1238</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>8908011797655</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>14626588</t>
-        </is>
+      <c r="G107" t="n">
+        <v>8908011797655</v>
+      </c>
+      <c r="H107" t="n">
+        <v>14626588</v>
       </c>
     </row>
     <row r="108">
@@ -3957,10 +3455,8 @@
       <c r="C108" t="n">
         <v>869</v>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D108" t="n">
+        <v>95030020</v>
       </c>
       <c r="E108" t="n">
         <v>0.05</v>
@@ -3970,10 +3466,8 @@
           <t>SMRT1240</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>8908011797624</t>
-        </is>
+      <c r="G108" t="n">
+        <v>8908011797624</v>
       </c>
     </row>
     <row r="109">
@@ -3988,10 +3482,8 @@
       <c r="C109" t="n">
         <v>969</v>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D109" t="n">
+        <v>95030020</v>
       </c>
       <c r="E109" t="n">
         <v>0.05</v>
@@ -4001,15 +3493,11 @@
           <t>SMRT1241</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>8908011797747</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>17856011</t>
-        </is>
+      <c r="G109" t="n">
+        <v>8908011797747</v>
+      </c>
+      <c r="H109" t="n">
+        <v>17856011</v>
       </c>
     </row>
     <row r="110">
@@ -4024,10 +3512,8 @@
       <c r="C110" t="n">
         <v>819</v>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D110" t="n">
+        <v>95030020</v>
       </c>
       <c r="E110" t="n">
         <v>0.05</v>
@@ -4037,20 +3523,14 @@
           <t>SMRT1242V2</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>8908011797679</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>15433823</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>480751</t>
-        </is>
+      <c r="G110" t="n">
+        <v>8908011797679</v>
+      </c>
+      <c r="H110" t="n">
+        <v>15433823</v>
+      </c>
+      <c r="I110" t="n">
+        <v>480751</v>
       </c>
     </row>
     <row r="111">
@@ -4065,10 +3545,8 @@
       <c r="C111" t="n">
         <v>899</v>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D111" t="n">
+        <v>95030020</v>
       </c>
       <c r="E111" t="n">
         <v>0.05</v>
@@ -4078,10 +3556,8 @@
           <t>SMRT1244</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>8908011797662</t>
-        </is>
+      <c r="G111" t="n">
+        <v>8908011797662</v>
       </c>
     </row>
     <row r="112">
@@ -4096,10 +3572,8 @@
       <c r="C112" t="n">
         <v>1699</v>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>95030010</t>
-        </is>
+      <c r="D112" t="n">
+        <v>95030010</v>
       </c>
       <c r="E112" t="n">
         <v>0.18</v>
@@ -4109,20 +3583,14 @@
           <t>SMRT1245</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>8908011797860</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>19825872</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>158421</t>
-        </is>
+      <c r="G112" t="n">
+        <v>8908011797860</v>
+      </c>
+      <c r="H112" t="n">
+        <v>19825872</v>
+      </c>
+      <c r="I112" t="n">
+        <v>158421</v>
       </c>
     </row>
     <row r="113">
@@ -4137,10 +3605,8 @@
       <c r="C113" t="n">
         <v>919</v>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D113" t="n">
+        <v>95030020</v>
       </c>
       <c r="E113" t="n">
         <v>0.05</v>
@@ -4150,10 +3616,8 @@
           <t>SMRT1246</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>8908011797723</t>
-        </is>
+      <c r="G113" t="n">
+        <v>8908011797723</v>
       </c>
     </row>
     <row r="114">
@@ -4168,10 +3632,8 @@
       <c r="C114" t="n">
         <v>769</v>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D114" t="n">
+        <v>95030020</v>
       </c>
       <c r="E114" t="n">
         <v>0.05</v>
@@ -4181,20 +3643,14 @@
           <t>SMRT1253</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>8908011797693</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>17856008</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>523050</t>
-        </is>
+      <c r="G114" t="n">
+        <v>8908011797693</v>
+      </c>
+      <c r="H114" t="n">
+        <v>17856008</v>
+      </c>
+      <c r="I114" t="n">
+        <v>523050</v>
       </c>
     </row>
     <row r="115">
@@ -4209,10 +3665,8 @@
       <c r="C115" t="n">
         <v>629</v>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D115" t="n">
+        <v>95030020</v>
       </c>
       <c r="E115" t="n">
         <v>0.05</v>
@@ -4222,10 +3676,8 @@
           <t>SMRT1254</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>8908011797709</t>
-        </is>
+      <c r="G115" t="n">
+        <v>8908011797709</v>
       </c>
     </row>
     <row r="116">
@@ -4240,10 +3692,8 @@
       <c r="C116" t="n">
         <v>999</v>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D116" t="n">
+        <v>95030020</v>
       </c>
       <c r="E116" t="n">
         <v>0.05</v>
@@ -4253,10 +3703,8 @@
           <t>SMRT1260</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>8908011797754</t>
-        </is>
+      <c r="G116" t="n">
+        <v>8908011797754</v>
       </c>
     </row>
     <row r="117">
@@ -4271,10 +3719,8 @@
       <c r="C117" t="n">
         <v>60</v>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D117" t="n">
+        <v>95030020</v>
       </c>
       <c r="E117" t="n">
         <v>0.05</v>
@@ -4284,10 +3730,8 @@
           <t>SMRT1262</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>8906187980031</t>
-        </is>
+      <c r="G117" t="n">
+        <v>8906187980031</v>
       </c>
     </row>
     <row r="118">
@@ -4302,10 +3746,8 @@
       <c r="C118" t="n">
         <v>669</v>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D118" t="n">
+        <v>95030020</v>
       </c>
       <c r="E118" t="n">
         <v>0.05</v>
@@ -4315,10 +3757,8 @@
           <t>SMRT1268</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>8908011797815</t>
-        </is>
+      <c r="G118" t="n">
+        <v>8908011797815</v>
       </c>
     </row>
     <row r="119">
@@ -4333,10 +3773,8 @@
       <c r="C119" t="n">
         <v>869</v>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D119" t="n">
+        <v>95030020</v>
       </c>
       <c r="E119" t="n">
         <v>0.05</v>
@@ -4346,15 +3784,11 @@
           <t>SMRT1269</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>8908011797822</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>891201</t>
-        </is>
+      <c r="G119" t="n">
+        <v>8908011797822</v>
+      </c>
+      <c r="I119" t="n">
+        <v>891201</v>
       </c>
     </row>
     <row r="120">
@@ -4369,10 +3803,8 @@
       <c r="C120" t="n">
         <v>769</v>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D120" t="n">
+        <v>95030020</v>
       </c>
       <c r="E120" t="n">
         <v>0.05</v>
@@ -4382,15 +3814,11 @@
           <t>SMRT1270</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>8908011797846</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>19825873</t>
-        </is>
+      <c r="G120" t="n">
+        <v>8908011797846</v>
+      </c>
+      <c r="H120" t="n">
+        <v>19825873</v>
       </c>
     </row>
     <row r="121">
@@ -4405,10 +3833,8 @@
       <c r="C121" t="n">
         <v>669</v>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D121" t="n">
+        <v>95030020</v>
       </c>
       <c r="E121" t="n">
         <v>0.05</v>
@@ -4418,10 +3844,8 @@
           <t>SMRT1271 - Mech Beas</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>8908011797761</t>
-        </is>
+      <c r="G121" t="n">
+        <v>8908011797761</v>
       </c>
     </row>
     <row r="122">
@@ -4436,10 +3860,8 @@
       <c r="C122" t="n">
         <v>299</v>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D122" t="n">
+        <v>95030020</v>
       </c>
       <c r="E122" t="n">
         <v>0.05</v>
@@ -4449,10 +3871,8 @@
           <t>SMRT1272</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>8908011797730</t>
-        </is>
+      <c r="G122" t="n">
+        <v>8908011797730</v>
       </c>
     </row>
     <row r="123">
@@ -4467,10 +3887,8 @@
       <c r="C123" t="n">
         <v>799</v>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D123" t="n">
+        <v>95030020</v>
       </c>
       <c r="E123" t="n">
         <v>0.05</v>
@@ -4480,15 +3898,11 @@
           <t>SMRT1273</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>8908011797938</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>645243</t>
-        </is>
+      <c r="G123" t="n">
+        <v>8908011797938</v>
+      </c>
+      <c r="I123" t="n">
+        <v>645243</v>
       </c>
     </row>
     <row r="124">
@@ -4503,10 +3917,8 @@
       <c r="C124" t="n">
         <v>869</v>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D124" t="n">
+        <v>95030020</v>
       </c>
       <c r="E124" t="n">
         <v>0.05</v>
@@ -4516,10 +3928,8 @@
           <t>SMRT1274</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>8908011797839</t>
-        </is>
+      <c r="G124" t="n">
+        <v>8908011797839</v>
       </c>
     </row>
     <row r="125">
@@ -4534,10 +3944,8 @@
       <c r="C125" t="n">
         <v>669</v>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D125" t="n">
+        <v>95030020</v>
       </c>
       <c r="E125" t="n">
         <v>0.05</v>
@@ -4547,10 +3955,8 @@
           <t>SMRT1275</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>8908011797778</t>
-        </is>
+      <c r="G125" t="n">
+        <v>8908011797778</v>
       </c>
     </row>
     <row r="126">
@@ -4565,10 +3971,8 @@
       <c r="C126" t="n">
         <v>649</v>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D126" t="n">
+        <v>95030020</v>
       </c>
       <c r="E126" t="n">
         <v>0.05</v>
@@ -4578,20 +3982,14 @@
           <t>SMRT1276</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>8908011797808</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>17856015</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>950782</t>
-        </is>
+      <c r="G126" t="n">
+        <v>8908011797808</v>
+      </c>
+      <c r="H126" t="n">
+        <v>17856015</v>
+      </c>
+      <c r="I126" t="n">
+        <v>950782</v>
       </c>
     </row>
     <row r="127">
@@ -4606,10 +4004,8 @@
       <c r="C127" t="n">
         <v>769</v>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D127" t="n">
+        <v>95030020</v>
       </c>
       <c r="E127" t="n">
         <v>0.05</v>
@@ -4619,15 +4015,11 @@
           <t>SMRT1277</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>8908011797853</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>18481804</t>
-        </is>
+      <c r="G127" t="n">
+        <v>8908011797853</v>
+      </c>
+      <c r="H127" t="n">
+        <v>18481804</v>
       </c>
     </row>
     <row r="128">
@@ -4642,10 +4034,8 @@
       <c r="C128" t="n">
         <v>849</v>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D128" t="n">
+        <v>95030020</v>
       </c>
       <c r="E128" t="n">
         <v>0.05</v>
@@ -4655,20 +4045,14 @@
           <t>SMRT1279</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>8908011797877</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>19050876</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>208840</t>
-        </is>
+      <c r="G128" t="n">
+        <v>8908011797877</v>
+      </c>
+      <c r="H128" t="n">
+        <v>19050876</v>
+      </c>
+      <c r="I128" t="n">
+        <v>208840</v>
       </c>
     </row>
     <row r="129">
@@ -4683,10 +4067,8 @@
       <c r="C129" t="n">
         <v>1099</v>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D129" t="n">
+        <v>95030020</v>
       </c>
       <c r="E129" t="n">
         <v>0.05</v>
@@ -4696,10 +4078,8 @@
           <t>SMRT1280</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>8908011797907</t>
-        </is>
+      <c r="G129" t="n">
+        <v>8908011797907</v>
       </c>
     </row>
     <row r="130">
@@ -4714,10 +4094,8 @@
       <c r="C130" t="n">
         <v>749</v>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D130" t="n">
+        <v>95030020</v>
       </c>
       <c r="E130" t="n">
         <v>0.05</v>
@@ -4727,15 +4105,11 @@
           <t>SMRT1281</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>8908011797891</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>18481805</t>
-        </is>
+      <c r="G130" t="n">
+        <v>8908011797891</v>
+      </c>
+      <c r="H130" t="n">
+        <v>18481805</v>
       </c>
     </row>
     <row r="131">
@@ -4750,10 +4124,8 @@
       <c r="C131" t="n">
         <v>579</v>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D131" t="n">
+        <v>95030020</v>
       </c>
       <c r="E131" t="n">
         <v>0.05</v>
@@ -4763,20 +4135,14 @@
           <t>SMRT1282</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>8908011797884</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>19825874</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>235066</t>
-        </is>
+      <c r="G131" t="n">
+        <v>8908011797884</v>
+      </c>
+      <c r="H131" t="n">
+        <v>19825874</v>
+      </c>
+      <c r="I131" t="n">
+        <v>235066</v>
       </c>
     </row>
     <row r="132">
@@ -4791,10 +4157,8 @@
       <c r="C132" t="n">
         <v>919</v>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D132" t="n">
+        <v>95030020</v>
       </c>
       <c r="E132" t="n">
         <v>0.05</v>
@@ -4804,10 +4168,8 @@
           <t>SMRT1283SM</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>8906187980079</t>
-        </is>
+      <c r="G132" t="n">
+        <v>8906187980079</v>
       </c>
     </row>
     <row r="133">
@@ -4822,10 +4184,8 @@
       <c r="C133" t="n">
         <v>289</v>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D133" t="n">
+        <v>95030020</v>
       </c>
       <c r="E133" t="n">
         <v>0.05</v>
@@ -4835,10 +4195,8 @@
           <t>SMRT1292</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>8908011797914</t>
-        </is>
+      <c r="G133" t="n">
+        <v>8908011797914</v>
       </c>
     </row>
     <row r="134">
@@ -4853,10 +4211,8 @@
       <c r="C134" t="n">
         <v>769</v>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D134" t="n">
+        <v>95030020</v>
       </c>
       <c r="E134" t="n">
         <v>0.05</v>
@@ -4866,15 +4222,11 @@
           <t>SMRT1293</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>8908011797952</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>19050877</t>
-        </is>
+      <c r="G134" t="n">
+        <v>8908011797952</v>
+      </c>
+      <c r="H134" t="n">
+        <v>19050877</v>
       </c>
     </row>
     <row r="135">
@@ -4889,10 +4241,8 @@
       <c r="C135" t="n">
         <v>749</v>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D135" t="n">
+        <v>95030020</v>
       </c>
       <c r="E135" t="n">
         <v>0.05</v>
@@ -4902,20 +4252,14 @@
           <t>SMRT1295</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>8906187980000</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>19287676</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>560273</t>
-        </is>
+      <c r="G135" t="n">
+        <v>8906187980000</v>
+      </c>
+      <c r="H135" t="n">
+        <v>19287676</v>
+      </c>
+      <c r="I135" t="n">
+        <v>560273</v>
       </c>
     </row>
     <row r="136">
@@ -4930,10 +4274,8 @@
       <c r="C136" t="n">
         <v>1299</v>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>95030010</t>
-        </is>
+      <c r="D136" t="n">
+        <v>95030010</v>
       </c>
       <c r="E136" t="n">
         <v>0.18</v>
@@ -4943,15 +4285,11 @@
           <t>SMRT1296</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>8906187980109</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>21239906</t>
-        </is>
+      <c r="G136" t="n">
+        <v>8906187980109</v>
+      </c>
+      <c r="H136" t="n">
+        <v>21239906</v>
       </c>
     </row>
     <row r="137">
@@ -4966,10 +4304,8 @@
       <c r="C137" t="n">
         <v>769</v>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D137" t="n">
+        <v>95030020</v>
       </c>
       <c r="E137" t="n">
         <v>0.05</v>
@@ -4979,10 +4315,8 @@
           <t>SMRT1297</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>8908011797983</t>
-        </is>
+      <c r="G137" t="n">
+        <v>8908011797983</v>
       </c>
     </row>
     <row r="138">
@@ -4997,10 +4331,8 @@
       <c r="C138" t="n">
         <v>799</v>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D138" t="n">
+        <v>95030020</v>
       </c>
       <c r="E138" t="n">
         <v>0.05</v>
@@ -5010,15 +4342,11 @@
           <t>SMRT1298</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>8908011797990</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>19825877</t>
-        </is>
+      <c r="G138" t="n">
+        <v>8908011797990</v>
+      </c>
+      <c r="H138" t="n">
+        <v>19825877</v>
       </c>
     </row>
     <row r="139">
@@ -5033,10 +4361,8 @@
       <c r="C139" t="n">
         <v>599</v>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D139" t="n">
+        <v>95030020</v>
       </c>
       <c r="E139" t="n">
         <v>0.05</v>
@@ -5046,20 +4372,14 @@
           <t>SMRT1299</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>8908011797969</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>19825875</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>864545</t>
-        </is>
+      <c r="G139" t="n">
+        <v>8908011797969</v>
+      </c>
+      <c r="H139" t="n">
+        <v>19825875</v>
+      </c>
+      <c r="I139" t="n">
+        <v>864545</v>
       </c>
     </row>
     <row r="140">
@@ -5074,10 +4394,8 @@
       <c r="C140" t="n">
         <v>699</v>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D140" t="n">
+        <v>95030020</v>
       </c>
       <c r="E140" t="n">
         <v>0.05</v>
@@ -5087,10 +4405,8 @@
           <t>SMRT1300</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>8906187980017</t>
-        </is>
+      <c r="G140" t="n">
+        <v>8906187980017</v>
       </c>
     </row>
     <row r="141">
@@ -5105,10 +4421,8 @@
       <c r="C141" t="n">
         <v>1099</v>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D141" t="n">
+        <v>95030020</v>
       </c>
       <c r="E141" t="n">
         <v>0.05</v>
@@ -5118,15 +4432,11 @@
           <t>SMRT1301</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>8906187980147</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>20586288</t>
-        </is>
+      <c r="G141" t="n">
+        <v>8906187980147</v>
+      </c>
+      <c r="H141" t="n">
+        <v>20586288</v>
       </c>
     </row>
     <row r="142">
@@ -5141,10 +4451,8 @@
       <c r="C142" t="n">
         <v>999</v>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>95030010</t>
-        </is>
+      <c r="D142" t="n">
+        <v>95030010</v>
       </c>
       <c r="E142" t="n">
         <v>0.18</v>
@@ -5154,15 +4462,11 @@
           <t>SMRT1302</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>8906187980178</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>20586289</t>
-        </is>
+      <c r="G142" t="n">
+        <v>8906187980178</v>
+      </c>
+      <c r="H142" t="n">
+        <v>20586289</v>
       </c>
     </row>
     <row r="143">
@@ -5177,10 +4481,8 @@
       <c r="C143" t="n">
         <v>1149</v>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D143" t="n">
+        <v>95030020</v>
       </c>
       <c r="E143" t="n">
         <v>0.05</v>
@@ -5190,20 +4492,14 @@
           <t>SMRT1303</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>8906187980345</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>22032971</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>822097</t>
-        </is>
+      <c r="G143" t="n">
+        <v>8906187980345</v>
+      </c>
+      <c r="H143" t="n">
+        <v>22032971</v>
+      </c>
+      <c r="I143" t="n">
+        <v>822097</v>
       </c>
     </row>
     <row r="144">
@@ -5218,10 +4514,8 @@
       <c r="C144" t="n">
         <v>869</v>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D144" t="n">
+        <v>95030020</v>
       </c>
       <c r="E144" t="n">
         <v>0.05</v>
@@ -5231,15 +4525,11 @@
           <t>SMRT1305</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>8906187980116</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>21239905</t>
-        </is>
+      <c r="G144" t="n">
+        <v>8906187980116</v>
+      </c>
+      <c r="H144" t="n">
+        <v>21239905</v>
       </c>
     </row>
     <row r="145">
@@ -5254,10 +4544,8 @@
       <c r="C145" t="n">
         <v>799</v>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D145" t="n">
+        <v>95030020</v>
       </c>
       <c r="E145" t="n">
         <v>0.05</v>
@@ -5267,15 +4555,11 @@
           <t>SMRT1309</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>8906187980222</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>21239909</t>
-        </is>
+      <c r="G145" t="n">
+        <v>8906187980222</v>
+      </c>
+      <c r="H145" t="n">
+        <v>21239909</v>
       </c>
     </row>
     <row r="146">
@@ -5290,10 +4574,8 @@
       <c r="C146" t="n">
         <v>749</v>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D146" t="n">
+        <v>95030020</v>
       </c>
       <c r="E146" t="n">
         <v>0.05</v>
@@ -5303,15 +4585,11 @@
           <t>SMRT1310</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>8906187980314</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>22032972</t>
-        </is>
+      <c r="G146" t="n">
+        <v>8906187980314</v>
+      </c>
+      <c r="H146" t="n">
+        <v>22032972</v>
       </c>
     </row>
     <row r="147">
@@ -5326,10 +4604,8 @@
       <c r="C147" t="n">
         <v>669</v>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D147" t="n">
+        <v>95030020</v>
       </c>
       <c r="E147" t="n">
         <v>0.05</v>
@@ -5339,15 +4615,11 @@
           <t>SMRT1312</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>8906187980208</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>21239907</t>
-        </is>
+      <c r="G147" t="n">
+        <v>8906187980208</v>
+      </c>
+      <c r="H147" t="n">
+        <v>21239907</v>
       </c>
     </row>
     <row r="148">
@@ -5362,10 +4634,8 @@
       <c r="C148" t="n">
         <v>549</v>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D148" t="n">
+        <v>95030020</v>
       </c>
       <c r="E148" t="n">
         <v>0.05</v>
@@ -5375,10 +4645,8 @@
           <t>SMRT1313</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>8906187980239</t>
-        </is>
+      <c r="G148" t="n">
+        <v>8906187980239</v>
       </c>
     </row>
     <row r="149">
@@ -5393,10 +4661,8 @@
       <c r="C149" t="n">
         <v>669</v>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D149" t="n">
+        <v>95030020</v>
       </c>
       <c r="E149" t="n">
         <v>0.05</v>
@@ -5406,15 +4672,11 @@
           <t>SMRT1315</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>8906187980215</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>21239908</t>
-        </is>
+      <c r="G149" t="n">
+        <v>8906187980215</v>
+      </c>
+      <c r="H149" t="n">
+        <v>21239908</v>
       </c>
     </row>
     <row r="150">
@@ -5429,10 +4691,8 @@
       <c r="C150" t="n">
         <v>599</v>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D150" t="n">
+        <v>95030020</v>
       </c>
       <c r="E150" t="n">
         <v>0.05</v>
@@ -5442,15 +4702,11 @@
           <t>SMRT1320</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>8906187980246</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>21239910</t>
-        </is>
+      <c r="G150" t="n">
+        <v>8906187980246</v>
+      </c>
+      <c r="H150" t="n">
+        <v>21239910</v>
       </c>
     </row>
     <row r="151">
@@ -5465,10 +4721,8 @@
       <c r="C151" t="n">
         <v>749</v>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D151" t="n">
+        <v>95030020</v>
       </c>
       <c r="E151" t="n">
         <v>0.05</v>
@@ -5478,15 +4732,11 @@
           <t>SMRT1321</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>8906187980260</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>21239911</t>
-        </is>
+      <c r="G151" t="n">
+        <v>8906187980260</v>
+      </c>
+      <c r="H151" t="n">
+        <v>21239911</v>
       </c>
     </row>
     <row r="152">
@@ -5501,10 +4751,8 @@
       <c r="C152" t="n">
         <v>799</v>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D152" t="n">
+        <v>95030020</v>
       </c>
       <c r="E152" t="n">
         <v>0.05</v>
@@ -5514,15 +4762,11 @@
           <t>SMRT1322</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>8906187980277</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>21239912</t>
-        </is>
+      <c r="G152" t="n">
+        <v>8906187980277</v>
+      </c>
+      <c r="H152" t="n">
+        <v>21239912</v>
       </c>
     </row>
     <row r="153">
@@ -5537,10 +4781,8 @@
       <c r="C153" t="n">
         <v>1499</v>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D153" t="n">
+        <v>95030020</v>
       </c>
       <c r="E153" t="n">
         <v>0.05</v>
@@ -5550,10 +4792,8 @@
           <t>SMRT1323</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>8906187980482</t>
-        </is>
+      <c r="G153" t="n">
+        <v>8906187980482</v>
       </c>
     </row>
     <row r="154">
@@ -5568,10 +4808,8 @@
       <c r="C154" t="n">
         <v>749</v>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D154" t="n">
+        <v>95030020</v>
       </c>
       <c r="E154" t="n">
         <v>0.05</v>
@@ -5581,15 +4819,11 @@
           <t>SMRT1324</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>8906187980321</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>22032969</t>
-        </is>
+      <c r="G154" t="n">
+        <v>8906187980321</v>
+      </c>
+      <c r="H154" t="n">
+        <v>22032969</v>
       </c>
     </row>
     <row r="155">
@@ -5604,10 +4838,8 @@
       <c r="C155" t="n">
         <v>899</v>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D155" t="n">
+        <v>95030020</v>
       </c>
       <c r="E155" t="n">
         <v>0.05</v>
@@ -5617,15 +4849,11 @@
           <t>SMRT1325</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>8906187980369</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>22032973</t>
-        </is>
+      <c r="G155" t="n">
+        <v>8906187980369</v>
+      </c>
+      <c r="H155" t="n">
+        <v>22032973</v>
       </c>
     </row>
     <row r="156">
@@ -5640,10 +4868,8 @@
       <c r="C156" t="n">
         <v>529</v>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D156" t="n">
+        <v>95030020</v>
       </c>
       <c r="E156" t="n">
         <v>0.05</v>
@@ -5653,10 +4879,8 @@
           <t>SMRT1326</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>8906187980253</t>
-        </is>
+      <c r="G156" t="n">
+        <v>8906187980253</v>
       </c>
     </row>
     <row r="157">
@@ -5671,10 +4895,8 @@
       <c r="C157" t="n">
         <v>699</v>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D157" t="n">
+        <v>95030020</v>
       </c>
       <c r="E157" t="n">
         <v>0.05</v>
@@ -5684,10 +4906,8 @@
           <t>SMRT1328</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>8906187980284</t>
-        </is>
+      <c r="G157" t="n">
+        <v>8906187980284</v>
       </c>
     </row>
     <row r="158">
@@ -5702,10 +4922,8 @@
       <c r="C158" t="n">
         <v>559</v>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D158" t="n">
+        <v>95030020</v>
       </c>
       <c r="E158" t="n">
         <v>0.05</v>
@@ -5715,10 +4933,8 @@
           <t>SMRT1329</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>8906187980291</t>
-        </is>
+      <c r="G158" t="n">
+        <v>8906187980291</v>
       </c>
     </row>
     <row r="159">
@@ -5733,10 +4949,8 @@
       <c r="C159" t="n">
         <v>699</v>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D159" t="n">
+        <v>95030020</v>
       </c>
       <c r="E159" t="n">
         <v>0.05</v>
@@ -5746,15 +4960,11 @@
           <t>SMRT1333</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>8906187980338</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>22032970</t>
-        </is>
+      <c r="G159" t="n">
+        <v>8906187980338</v>
+      </c>
+      <c r="H159" t="n">
+        <v>22032970</v>
       </c>
     </row>
     <row r="160">
@@ -5769,10 +4979,8 @@
       <c r="C160" t="n">
         <v>1149</v>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D160" t="n">
+        <v>95030020</v>
       </c>
       <c r="E160" t="n">
         <v>0.05</v>
@@ -5782,15 +4990,11 @@
           <t>SMRT1334</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>8906187980376</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>22032974</t>
-        </is>
+      <c r="G160" t="n">
+        <v>8906187980376</v>
+      </c>
+      <c r="H160" t="n">
+        <v>22032974</v>
       </c>
     </row>
     <row r="161">
@@ -5805,10 +5009,8 @@
       <c r="C161" t="n">
         <v>649</v>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D161" t="n">
+        <v>95030020</v>
       </c>
       <c r="E161" t="n">
         <v>0.05</v>
@@ -5818,10 +5020,8 @@
           <t>SMRT1335</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>8906187980383</t>
-        </is>
+      <c r="G161" t="n">
+        <v>8906187980383</v>
       </c>
     </row>
     <row r="162">
@@ -5836,10 +5036,8 @@
       <c r="C162" t="n">
         <v>699</v>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D162" t="n">
+        <v>95030020</v>
       </c>
       <c r="E162" t="n">
         <v>0.05</v>
@@ -5849,15 +5047,11 @@
           <t>SMRT1336</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>8906187980307</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>21239913</t>
-        </is>
+      <c r="G162" t="n">
+        <v>8906187980307</v>
+      </c>
+      <c r="H162" t="n">
+        <v>21239913</v>
       </c>
     </row>
     <row r="163">
@@ -5872,10 +5066,8 @@
       <c r="C163" t="n">
         <v>749</v>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D163" t="n">
+        <v>95030020</v>
       </c>
       <c r="E163" t="n">
         <v>0.05</v>
@@ -5885,15 +5077,11 @@
           <t>SMRT1337</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>8906187980352</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>22032975</t>
-        </is>
+      <c r="G163" t="n">
+        <v>8906187980352</v>
+      </c>
+      <c r="H163" t="n">
+        <v>22032975</v>
       </c>
     </row>
     <row r="164">
@@ -5908,10 +5096,8 @@
       <c r="C164" t="n">
         <v>699</v>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D164" t="n">
+        <v>95030020</v>
       </c>
       <c r="E164" t="n">
         <v>0.05</v>
@@ -5921,15 +5107,11 @@
           <t>SMRT1339</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>8906187980413</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>22032978</t>
-        </is>
+      <c r="G164" t="n">
+        <v>8906187980413</v>
+      </c>
+      <c r="H164" t="n">
+        <v>22032978</v>
       </c>
     </row>
     <row r="165">
@@ -5944,10 +5126,8 @@
       <c r="C165" t="n">
         <v>599</v>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D165" t="n">
+        <v>95030020</v>
       </c>
       <c r="E165" t="n">
         <v>0.05</v>
@@ -5957,15 +5137,11 @@
           <t>SMRT1340</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>8906187980390</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>22032977</t>
-        </is>
+      <c r="G165" t="n">
+        <v>8906187980390</v>
+      </c>
+      <c r="H165" t="n">
+        <v>22032977</v>
       </c>
     </row>
     <row r="166">
@@ -5980,10 +5156,8 @@
       <c r="C166" t="n">
         <v>899</v>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D166" t="n">
+        <v>95030020</v>
       </c>
       <c r="E166" t="n">
         <v>0.05</v>
@@ -5993,10 +5167,8 @@
           <t>SMRT1344</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>8906187980475</t>
-        </is>
+      <c r="G166" t="n">
+        <v>8906187980475</v>
       </c>
     </row>
     <row r="167">
@@ -6011,10 +5183,8 @@
       <c r="C167" t="n">
         <v>1099</v>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D167" t="n">
+        <v>95030020</v>
       </c>
       <c r="E167" t="n">
         <v>0.05</v>
@@ -6024,10 +5194,8 @@
           <t>SMRT1345</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>8906187980468</t>
-        </is>
+      <c r="G167" t="n">
+        <v>8906187980468</v>
       </c>
     </row>
     <row r="168">
@@ -6042,10 +5210,8 @@
       <c r="C168" t="n">
         <v>699</v>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D168" t="n">
+        <v>95030020</v>
       </c>
       <c r="E168" t="n">
         <v>0.05</v>
@@ -6055,15 +5221,11 @@
           <t>SMRT1346</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>8906187980420</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>22032979</t>
-        </is>
+      <c r="G168" t="n">
+        <v>8906187980420</v>
+      </c>
+      <c r="H168" t="n">
+        <v>22032979</v>
       </c>
     </row>
     <row r="169">
@@ -6078,10 +5240,8 @@
       <c r="C169" t="n">
         <v>799</v>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D169" t="n">
+        <v>95030020</v>
       </c>
       <c r="E169" t="n">
         <v>0.05</v>
@@ -6091,10 +5251,8 @@
           <t>SMRT1347</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>8906187980444</t>
-        </is>
+      <c r="G169" t="n">
+        <v>8906187980444</v>
       </c>
     </row>
     <row r="170">
@@ -6109,10 +5267,8 @@
       <c r="C170" t="n">
         <v>799</v>
       </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D170" t="n">
+        <v>95030020</v>
       </c>
       <c r="E170" t="n">
         <v>0.05</v>
@@ -6122,10 +5278,8 @@
           <t>SMRT1348</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>8906187980451</t>
-        </is>
+      <c r="G170" t="n">
+        <v>8906187980451</v>
       </c>
     </row>
     <row r="171">
@@ -6140,10 +5294,8 @@
       <c r="C171" t="n">
         <v>849</v>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D171" t="n">
+        <v>95030020</v>
       </c>
       <c r="E171" t="n">
         <v>0.05</v>
@@ -6153,10 +5305,8 @@
           <t>SMRT1364</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>8906187980512</t>
-        </is>
+      <c r="G171" t="n">
+        <v>8906187980512</v>
       </c>
     </row>
     <row r="172">
@@ -6171,10 +5321,8 @@
       <c r="C172" t="n">
         <v>1199</v>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D172" t="n">
+        <v>95030020</v>
       </c>
       <c r="E172" t="n">
         <v>0.05</v>
@@ -6184,10 +5332,8 @@
           <t>SMRT1350</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>8906187980536</t>
-        </is>
+      <c r="G172" t="n">
+        <v>8906187980536</v>
       </c>
     </row>
     <row r="173">
@@ -6202,10 +5348,8 @@
       <c r="C173" t="n">
         <v>349</v>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D173" t="n">
+        <v>95030020</v>
       </c>
       <c r="E173" t="n">
         <v>0.05</v>
@@ -6215,10 +5359,8 @@
           <t>SMRT1358</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>8906187980628</t>
-        </is>
+      <c r="G173" t="n">
+        <v>8906187980628</v>
       </c>
     </row>
     <row r="174">
@@ -6233,10 +5375,8 @@
       <c r="C174" t="n">
         <v>299</v>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D174" t="n">
+        <v>95030020</v>
       </c>
       <c r="E174" t="n">
         <v>0.05</v>
@@ -6246,10 +5386,8 @@
           <t>SMRT1360</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>8906187980635</t>
-        </is>
+      <c r="G174" t="n">
+        <v>8906187980635</v>
       </c>
     </row>
     <row r="175">
@@ -6264,10 +5402,8 @@
       <c r="C175" t="n">
         <v>799</v>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>95030020</t>
-        </is>
+      <c r="D175" t="n">
+        <v>95030020</v>
       </c>
       <c r="E175" t="n">
         <v>0.05</v>
@@ -6277,10 +5413,8 @@
           <t>SMRT1369</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>8906187980666</t>
-        </is>
+      <c r="G175" t="n">
+        <v>8906187980666</v>
       </c>
     </row>
     <row r="176">
@@ -6337,6 +5471,7 @@
         <v>8906187980505</v>
       </c>
     </row>
+    <row r="178"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5471,7 +5471,33 @@
         <v>8906187980505</v>
       </c>
     </row>
-    <row r="178"/>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>178</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SMRT1200</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D178" t="n">
+        <v>95030020</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>SMRT1200</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>8906112345672</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I178"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5469,33 +5469,6 @@
       </c>
       <c r="G177" t="n">
         <v>8906187980505</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>178</v>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>SMRT1200</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D178" t="n">
-        <v>95030020</v>
-      </c>
-      <c r="E178" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>SMRT1200</t>
-        </is>
-      </c>
-      <c r="G178" t="n">
-        <v>8906112345672</v>
       </c>
     </row>
   </sheetData>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:I178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5469,6 +5469,33 @@
       </c>
       <c r="G177" t="n">
         <v>8906187980505</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>178</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SMRT1200</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D178" t="n">
+        <v>95030020</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>SMRT1200</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>8906112345672</v>
       </c>
     </row>
   </sheetData>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Price list" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="discount" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price list" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="discount" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6525,6 +6525,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PRINCE ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PRINCE ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.5089</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.5089</v>
+        <v>0.4738</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.4738</v>
+        <v>0.4762</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6549,6 +6549,25 @@
         <v>0</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>KIDS JUNCTION</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price list" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="discount" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Price list" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="discount" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6555,6 +6555,11 @@
           <t>KIDS JUNCTION</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>KIDS JUNCTION</t>
+        </is>
+      </c>
       <c r="C45" t="n">
         <v>0.4286</v>
       </c>
@@ -6565,6 +6570,78 @@
         <v>0.4915</v>
       </c>
       <c r="F45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SATNAM MARKETING</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SATNAM MARKETING</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ramdev Extension</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ramdev Extension</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T G ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>T G ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F48" t="n">
         <v>0</v>
       </c>
     </row>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6645,6 +6645,54 @@
         <v>0</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>RAMDEV IMPEX</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>RAMDEV IMPEX</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CENTER ONE ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CENTER ONE ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6693,6 +6693,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BLISS ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BLISS ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
